--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423604</v>
+        <v>129424010</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560085</v>
+        <v>560054</v>
       </c>
       <c r="R2" t="n">
-        <v>7064313</v>
+        <v>7064358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129423507</v>
+        <v>129423604</v>
       </c>
       <c r="B3" t="n">
-        <v>56908</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560106</v>
+        <v>560085</v>
       </c>
       <c r="R3" t="n">
-        <v>7064289</v>
+        <v>7064313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129424010</v>
+        <v>129423507</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>56908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560054</v>
+        <v>560106</v>
       </c>
       <c r="R4" t="n">
-        <v>7064358</v>
+        <v>7064289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>129427285</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,49 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129424015</v>
+        <v>129427283</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560049</v>
+        <v>559968</v>
       </c>
       <c r="R6" t="n">
-        <v>7064357</v>
+        <v>7064298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,19 +1166,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,62 +1183,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129422931</v>
+        <v>129424015</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560279</v>
+        <v>560049</v>
       </c>
       <c r="R7" t="n">
-        <v>7064267</v>
+        <v>7064357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1269,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1294,12 +1279,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1309,7 @@
         <v>129427243</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129427283</v>
+        <v>129422931</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,34 +1414,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559968</v>
+        <v>560279</v>
       </c>
       <c r="R9" t="n">
-        <v>7064298</v>
+        <v>7064267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,9 +1476,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,12 +1508,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
         <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>129427286</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129424172</v>
+        <v>129427249</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560042</v>
+        <v>560236</v>
       </c>
       <c r="R12" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,19 +1787,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,22 +1809,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,21 +1832,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R13" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,17 +1889,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1928,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427267</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>91959</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,16 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560309</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
-        <v>7064195</v>
+        <v>7064186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,7 +1993,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2021,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427264</v>
+        <v>129424172</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,34 +2022,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560192</v>
+        <v>560042</v>
       </c>
       <c r="R15" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,9 +2079,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
         <v>129422438</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427256</v>
+        <v>129427282</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560241</v>
+        <v>560033</v>
       </c>
       <c r="R17" t="n">
-        <v>7064201</v>
+        <v>7064272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2325,7 @@
         <v>129427271</v>
       </c>
       <c r="B18" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427260</v>
+        <v>129427256</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559954</v>
+        <v>560241</v>
       </c>
       <c r="R19" t="n">
-        <v>7064373</v>
+        <v>7064201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427282</v>
+        <v>129427260</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R20" t="n">
-        <v>7064272</v>
+        <v>7064373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,6 +2592,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129419985</v>
+        <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,17 +2654,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560212</v>
+        <v>560090</v>
       </c>
       <c r="R21" t="n">
-        <v>7064155</v>
+        <v>7064325</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2691,19 +2691,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,22 +2708,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427287</v>
+        <v>129419985</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,17 +2751,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560090</v>
+        <v>560212</v>
       </c>
       <c r="R22" t="n">
-        <v>7064325</v>
+        <v>7064155</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2798,9 +2788,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,12 +2815,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
         <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,45 +2929,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>91996</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R24" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,19 +2997,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,12 +3014,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3039,7 +3029,7 @@
         <v>129427263</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,45 +3123,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427254</v>
+        <v>129424097</v>
       </c>
       <c r="B26" t="n">
-        <v>91993</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560321</v>
+        <v>560066</v>
       </c>
       <c r="R26" t="n">
-        <v>7064226</v>
+        <v>7064318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,9 +3191,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
         <v>129424195</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>129427235</v>
       </c>
       <c r="B28" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129422764</v>
+        <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,39 +3449,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560316</v>
+        <v>560320</v>
       </c>
       <c r="R29" t="n">
-        <v>7064209</v>
+        <v>7064230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3511,24 +3506,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3543,22 +3523,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129427242</v>
+        <v>129422764</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,34 +3546,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560320</v>
+        <v>560316</v>
       </c>
       <c r="R30" t="n">
-        <v>7064230</v>
+        <v>7064209</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3623,9 +3608,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3640,12 +3640,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
         <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>96956</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>96952</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,57 +4043,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129420535</v>
+        <v>129427246</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>80177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560216</v>
+        <v>560192</v>
       </c>
       <c r="R35" t="n">
-        <v>7064197</v>
+        <v>7064186</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,19 +4123,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4150,12 +4140,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4165,7 +4155,7 @@
         <v>129423749</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4269,10 +4259,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129422985</v>
+        <v>129420535</v>
       </c>
       <c r="B37" t="n">
-        <v>91536</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4280,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4304,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560263</v>
+        <v>560216</v>
       </c>
       <c r="R37" t="n">
-        <v>7064243</v>
+        <v>7064197</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4339,7 +4329,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4349,7 +4339,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4376,49 +4366,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129424136</v>
+        <v>129422985</v>
       </c>
       <c r="B38" t="n">
-        <v>98706</v>
+        <v>91539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560048</v>
+        <v>560263</v>
       </c>
       <c r="R38" t="n">
-        <v>7064312</v>
+        <v>7064243</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,7 +4436,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4460,7 +4446,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427246</v>
+        <v>129427240</v>
       </c>
       <c r="B39" t="n">
-        <v>80175</v>
+        <v>91507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,21 +4484,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4522,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560192</v>
+        <v>560201</v>
       </c>
       <c r="R39" t="n">
-        <v>7064186</v>
+        <v>7064160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,45 +4570,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129427240</v>
+        <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>91504</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560201</v>
+        <v>560048</v>
       </c>
       <c r="R40" t="n">
-        <v>7064160</v>
+        <v>7064312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,9 +4642,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,12 +4669,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4684,7 +4684,7 @@
         <v>129427288</v>
       </c>
       <c r="B41" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4895,49 +4895,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129423125</v>
+        <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560204</v>
+        <v>560200</v>
       </c>
       <c r="R43" t="n">
-        <v>7064212</v>
+        <v>7064167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,19 +4963,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4994,61 +4980,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129423615</v>
+        <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>98706</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560077</v>
+        <v>560192</v>
       </c>
       <c r="R44" t="n">
-        <v>7064315</v>
+        <v>7064186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5078,19 +5060,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5105,22 +5077,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427257</v>
+        <v>129427268</v>
       </c>
       <c r="B45" t="n">
-        <v>91838</v>
+        <v>78800</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5128,21 +5100,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5152,10 +5124,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560200</v>
+        <v>559964</v>
       </c>
       <c r="R45" t="n">
-        <v>7064167</v>
+        <v>7064339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5214,37 +5186,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427273</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>98706</v>
+        <v>57831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5253,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560001</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064286</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,7 +5269,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5316,45 +5287,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427265</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>80182</v>
+        <v>98710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560192</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064186</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5395,6 +5370,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5413,45 +5389,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427268</v>
+        <v>129423615</v>
       </c>
       <c r="B48" t="n">
-        <v>78798</v>
+        <v>98710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>559964</v>
+        <v>560077</v>
       </c>
       <c r="R48" t="n">
-        <v>7064339</v>
+        <v>7064315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5481,9 +5461,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5498,61 +5488,61 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427266</v>
+        <v>129423125</v>
       </c>
       <c r="B49" t="n">
-        <v>57831</v>
+        <v>98710</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560311</v>
+        <v>560204</v>
       </c>
       <c r="R49" t="n">
-        <v>7064217</v>
+        <v>7064212</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,9 +5572,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,62 +5599,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>92261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R50" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5681,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5696,7 +5691,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5723,34 +5718,30 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>92258</v>
+        <v>91563</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5758,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R51" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5793,7 +5784,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5803,7 +5794,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5830,49 +5821,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129423514</v>
+        <v>129422827</v>
       </c>
       <c r="B52" t="n">
-        <v>98706</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560095</v>
+        <v>560315</v>
       </c>
       <c r="R52" t="n">
-        <v>7064302</v>
+        <v>7064259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5904,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5914,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5941,41 +5933,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>91560</v>
+        <v>98710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R53" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,45 +1098,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427283</v>
+        <v>129424015</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559968</v>
+        <v>560049</v>
       </c>
       <c r="R6" t="n">
-        <v>7064298</v>
+        <v>7064357</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1170,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,61 +1197,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129424015</v>
+        <v>129427243</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560049</v>
+        <v>560198</v>
       </c>
       <c r="R7" t="n">
-        <v>7064357</v>
+        <v>7064162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,19 +1277,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,22 +1294,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B8" t="n">
-        <v>91543</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R8" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R12" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,17 +1787,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427267</v>
+        <v>129427264</v>
       </c>
       <c r="B13" t="n">
-        <v>91962</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,16 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560309</v>
+        <v>560192</v>
       </c>
       <c r="R13" t="n">
-        <v>7064195</v>
+        <v>7064186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,7 +1891,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129424172</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,34 +1920,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560042</v>
       </c>
       <c r="R14" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,9 +1977,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129424172</v>
+        <v>129427249</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,34 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560042</v>
+        <v>560236</v>
       </c>
       <c r="R15" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,19 +2084,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2929,32 +2929,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R24" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B25" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,34 +3037,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R25" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,9 +3094,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3111,57 +3121,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>91996</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R26" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,19 +3201,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,61 +3218,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129424195</v>
+        <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>96956</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560020</v>
+        <v>560199</v>
       </c>
       <c r="R27" t="n">
-        <v>7064291</v>
+        <v>7064182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3302,19 +3298,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3329,57 +3315,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129427235</v>
+        <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>96956</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560199</v>
+        <v>560020</v>
       </c>
       <c r="R28" t="n">
-        <v>7064182</v>
+        <v>7064291</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3409,9 +3399,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4055,45 +4055,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129427246</v>
+        <v>129422985</v>
       </c>
       <c r="B35" t="n">
-        <v>80177</v>
+        <v>91539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560192</v>
+        <v>560263</v>
       </c>
       <c r="R35" t="n">
-        <v>7064186</v>
+        <v>7064243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,9 +4123,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,57 +4150,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B36" t="n">
-        <v>80148</v>
+        <v>80177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R36" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,19 +4230,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,22 +4247,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,34 +4270,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R37" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129422985</v>
+        <v>129420535</v>
       </c>
       <c r="B38" t="n">
-        <v>91539</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560263</v>
+        <v>560216</v>
       </c>
       <c r="R38" t="n">
-        <v>7064243</v>
+        <v>7064197</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4895,45 +4895,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427257</v>
+        <v>129423125</v>
       </c>
       <c r="B43" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560200</v>
+        <v>560204</v>
       </c>
       <c r="R43" t="n">
-        <v>7064167</v>
+        <v>7064212</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4963,9 +4967,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4980,44 +4994,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427265</v>
+        <v>129427257</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>91841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560192</v>
+        <v>560200</v>
       </c>
       <c r="R44" t="n">
-        <v>7064186</v>
+        <v>7064167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,45 +5103,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427268</v>
+        <v>129427266</v>
       </c>
       <c r="B45" t="n">
-        <v>78800</v>
+        <v>57831</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559964</v>
+        <v>560311</v>
       </c>
       <c r="R45" t="n">
-        <v>7064339</v>
+        <v>7064217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,10 +5204,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129427265</v>
       </c>
       <c r="B46" t="n">
-        <v>57831</v>
+        <v>80184</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5197,38 +5215,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560192</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064186</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,49 +5301,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427273</v>
+        <v>129427268</v>
       </c>
       <c r="B47" t="n">
-        <v>98710</v>
+        <v>78800</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560001</v>
+        <v>559964</v>
       </c>
       <c r="R47" t="n">
-        <v>7064286</v>
+        <v>7064339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5370,7 +5380,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5389,7 +5398,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423615</v>
+        <v>129427273</v>
       </c>
       <c r="B48" t="n">
         <v>98710</v>
@@ -5419,19 +5428,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560077</v>
+        <v>560001</v>
       </c>
       <c r="R48" t="n">
-        <v>7064315</v>
+        <v>7064286</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,46 +5470,37 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B49" t="n">
         <v>98710</v>
@@ -5530,19 +5530,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R49" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5611,34 +5611,30 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B50" t="n">
-        <v>92261</v>
+        <v>91563</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5646,10 +5642,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R50" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,7 +5677,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5691,7 +5687,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5718,10 +5714,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422999</v>
+        <v>129422827</v>
       </c>
       <c r="B51" t="n">
-        <v>91563</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5729,30 +5725,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560298</v>
+        <v>560315</v>
       </c>
       <c r="R51" t="n">
-        <v>7064242</v>
+        <v>7064259</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,7 +5789,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5794,7 +5799,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5821,50 +5826,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422827</v>
+        <v>129423514</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>98710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560315</v>
+        <v>560095</v>
       </c>
       <c r="R52" t="n">
-        <v>7064259</v>
+        <v>7064302</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5900,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5910,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5933,49 +5937,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129423514</v>
+        <v>129421945</v>
       </c>
       <c r="B53" t="n">
-        <v>98710</v>
+        <v>92261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560095</v>
+        <v>560235</v>
       </c>
       <c r="R53" t="n">
-        <v>7064302</v>
+        <v>7064180</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129424010</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129423604</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129427285</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,49 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129424015</v>
+        <v>129427243</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560049</v>
+        <v>560198</v>
       </c>
       <c r="R6" t="n">
-        <v>7064357</v>
+        <v>7064162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,19 +1166,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,57 +1183,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427243</v>
+        <v>129424015</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560198</v>
+        <v>560049</v>
       </c>
       <c r="R7" t="n">
-        <v>7064162</v>
+        <v>7064357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,9 +1267,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,57 +1294,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427283</v>
+        <v>129427269</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559968</v>
+        <v>560091</v>
       </c>
       <c r="R8" t="n">
-        <v>7064298</v>
+        <v>7064300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129422931</v>
+        <v>129427283</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,39 +1419,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560279</v>
+        <v>559968</v>
       </c>
       <c r="R9" t="n">
-        <v>7064267</v>
+        <v>7064298</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,24 +1476,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,61 +1493,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129427269</v>
+        <v>129422931</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560091</v>
+        <v>560279</v>
       </c>
       <c r="R10" t="n">
-        <v>7064300</v>
+        <v>7064267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,30 +1578,44 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
         <v>129427286</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427267</v>
+        <v>129424172</v>
       </c>
       <c r="B12" t="n">
-        <v>91962</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,29 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560309</v>
+        <v>560042</v>
       </c>
       <c r="R12" t="n">
-        <v>7064195</v>
+        <v>7064308</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,40 +1787,49 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B13" t="n">
-        <v>80148</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,7 +1861,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R13" t="n">
         <v>7064186</v>
@@ -1883,6 +1897,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129424172</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,34 +1939,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560042</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,19 +1996,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,22 +2013,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>91964</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,21 +2036,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R15" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,17 +2093,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129422438</v>
+        <v>129427282</v>
       </c>
       <c r="B16" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560245</v>
+        <v>560033</v>
       </c>
       <c r="R16" t="n">
-        <v>7064205</v>
+        <v>7064272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,19 +2186,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427282</v>
+        <v>129427256</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>91843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560033</v>
+        <v>560241</v>
       </c>
       <c r="R17" t="n">
-        <v>7064272</v>
+        <v>7064201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,49 +2312,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427271</v>
+        <v>129422438</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560086</v>
+        <v>560245</v>
       </c>
       <c r="R18" t="n">
-        <v>7064325</v>
+        <v>7064205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,40 +2380,49 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427256</v>
+        <v>129427260</v>
       </c>
       <c r="B19" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560241</v>
+        <v>559954</v>
       </c>
       <c r="R19" t="n">
-        <v>7064201</v>
+        <v>7064373</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,45 +2521,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R20" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,17 +2598,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129419985</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R24" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,9 +2997,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3014,22 +3024,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129424097</v>
+        <v>129427263</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,34 +3047,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560066</v>
+        <v>560037</v>
       </c>
       <c r="R25" t="n">
-        <v>7064318</v>
+        <v>7064364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,19 +3104,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,12 +3121,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
         <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,45 +3230,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129427235</v>
+        <v>129424195</v>
       </c>
       <c r="B27" t="n">
-        <v>96956</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560199</v>
+        <v>560020</v>
       </c>
       <c r="R27" t="n">
-        <v>7064182</v>
+        <v>7064291</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,9 +3302,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3315,61 +3329,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129424195</v>
+        <v>129427235</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>96958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560020</v>
+        <v>560199</v>
       </c>
       <c r="R28" t="n">
-        <v>7064291</v>
+        <v>7064182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,19 +3409,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
         <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>96956</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>96958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,22 +4043,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129422985</v>
+        <v>129423749</v>
       </c>
       <c r="B35" t="n">
-        <v>91539</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560263</v>
+        <v>560086</v>
       </c>
       <c r="R35" t="n">
-        <v>7064243</v>
+        <v>7064365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4162,45 +4162,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427246</v>
+        <v>129424136</v>
       </c>
       <c r="B36" t="n">
-        <v>80177</v>
+        <v>98712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560192</v>
+        <v>560048</v>
       </c>
       <c r="R36" t="n">
-        <v>7064186</v>
+        <v>7064312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,9 +4234,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,57 +4261,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B37" t="n">
-        <v>80148</v>
+        <v>80178</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R37" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,19 +4341,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,12 +4358,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4369,7 +4373,7 @@
         <v>129420535</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,45 +4477,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427240</v>
+        <v>129422985</v>
       </c>
       <c r="B39" t="n">
-        <v>91507</v>
+        <v>91541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560201</v>
+        <v>560263</v>
       </c>
       <c r="R39" t="n">
-        <v>7064160</v>
+        <v>7064243</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4541,9 +4545,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,61 +4572,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129424136</v>
+        <v>129427240</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>91509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560048</v>
+        <v>560201</v>
       </c>
       <c r="R40" t="n">
-        <v>7064312</v>
+        <v>7064160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4642,19 +4652,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,12 +4669,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4684,7 +4684,7 @@
         <v>129427288</v>
       </c>
       <c r="B41" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4895,49 +4895,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129423125</v>
+        <v>129427265</v>
       </c>
       <c r="B43" t="n">
-        <v>98710</v>
+        <v>80185</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560204</v>
+        <v>560192</v>
       </c>
       <c r="R43" t="n">
-        <v>7064212</v>
+        <v>7064186</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,19 +4963,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4994,22 +4980,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427257</v>
+        <v>129427268</v>
       </c>
       <c r="B44" t="n">
-        <v>91841</v>
+        <v>78801</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5003,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560200</v>
+        <v>559964</v>
       </c>
       <c r="R44" t="n">
-        <v>7064167</v>
+        <v>7064339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,49 +5089,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427266</v>
+        <v>129427257</v>
       </c>
       <c r="B45" t="n">
-        <v>57831</v>
+        <v>91843</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560311</v>
+        <v>560200</v>
       </c>
       <c r="R45" t="n">
-        <v>7064217</v>
+        <v>7064167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5204,10 +5186,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427265</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>80184</v>
+        <v>57831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5215,34 +5197,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560192</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064186</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5301,45 +5287,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427268</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>78800</v>
+        <v>98712</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>559964</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064339</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,6 +5370,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5398,10 +5389,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427273</v>
+        <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5428,19 +5419,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560001</v>
+        <v>560204</v>
       </c>
       <c r="R48" t="n">
-        <v>7064286</v>
+        <v>7064212</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5470,30 +5461,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5503,7 +5503,7 @@
         <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5611,30 +5611,34 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422999</v>
+        <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>91563</v>
+        <v>92263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5642,10 +5646,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560298</v>
+        <v>560235</v>
       </c>
       <c r="R50" t="n">
-        <v>7064242</v>
+        <v>7064180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5677,7 +5681,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5687,7 +5691,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5714,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422827</v>
+        <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>91565</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5725,39 +5729,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560315</v>
+        <v>560298</v>
       </c>
       <c r="R51" t="n">
-        <v>7064259</v>
+        <v>7064242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5789,7 +5784,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5799,7 +5794,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5826,49 +5821,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129423514</v>
+        <v>129422827</v>
       </c>
       <c r="B52" t="n">
-        <v>98710</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560095</v>
+        <v>560315</v>
       </c>
       <c r="R52" t="n">
-        <v>7064302</v>
+        <v>7064259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5900,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5910,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5937,45 +5933,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129421945</v>
+        <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>92261</v>
+        <v>98712</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560235</v>
+        <v>560095</v>
       </c>
       <c r="R53" t="n">
-        <v>7064180</v>
+        <v>7064302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>129427243</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>129424015</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129427269</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129424172</v>
+        <v>129427264</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560042</v>
+        <v>560192</v>
       </c>
       <c r="R12" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,19 +1787,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1928,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129424172</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,34 +1929,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560042</v>
       </c>
       <c r="R14" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,9 +1986,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,12 +2013,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2028,7 +2028,7 @@
         <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>91964</v>
+        <v>91968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,45 +2118,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427282</v>
+        <v>129427271</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560033</v>
+        <v>560086</v>
       </c>
       <c r="R16" t="n">
-        <v>7064272</v>
+        <v>7064325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2201,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2215,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427256</v>
+        <v>129427282</v>
       </c>
       <c r="B17" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560241</v>
+        <v>560033</v>
       </c>
       <c r="R17" t="n">
-        <v>7064201</v>
+        <v>7064272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B18" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2328,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R18" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,19 +2385,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,12 +2402,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2521,49 +2516,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427271</v>
+        <v>129422438</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560086</v>
+        <v>560245</v>
       </c>
       <c r="R20" t="n">
-        <v>7064325</v>
+        <v>7064205</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,30 +2584,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
         <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,45 +2929,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>92002</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R24" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,19 +2997,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,12 +3014,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3133,45 +3123,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427254</v>
+        <v>129424097</v>
       </c>
       <c r="B26" t="n">
-        <v>91998</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560321</v>
+        <v>560066</v>
       </c>
       <c r="R26" t="n">
-        <v>7064226</v>
+        <v>7064318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,9 +3191,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
         <v>129424195</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>129427235</v>
       </c>
       <c r="B28" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>96962</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>96958</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,22 +4043,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129423749</v>
+        <v>129422985</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>91545</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560086</v>
+        <v>560263</v>
       </c>
       <c r="R35" t="n">
-        <v>7064365</v>
+        <v>7064243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4162,49 +4162,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129424136</v>
+        <v>129427240</v>
       </c>
       <c r="B36" t="n">
-        <v>98712</v>
+        <v>91513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560048</v>
+        <v>560201</v>
       </c>
       <c r="R36" t="n">
-        <v>7064312</v>
+        <v>7064160</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4234,19 +4230,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4261,12 +4247,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4370,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4381,34 +4367,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R38" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4440,7 +4426,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4450,7 +4436,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4477,10 +4463,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129422985</v>
+        <v>129420535</v>
       </c>
       <c r="B39" t="n">
-        <v>91541</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4488,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4512,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560263</v>
+        <v>560216</v>
       </c>
       <c r="R39" t="n">
-        <v>7064243</v>
+        <v>7064197</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,7 +4533,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4557,7 +4543,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,45 +4570,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129427240</v>
+        <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>91509</v>
+        <v>98716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560201</v>
+        <v>560048</v>
       </c>
       <c r="R40" t="n">
-        <v>7064160</v>
+        <v>7064312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,9 +4642,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,12 +4669,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4895,32 +4895,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427265</v>
+        <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>80185</v>
+        <v>91847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560192</v>
+        <v>560200</v>
       </c>
       <c r="R43" t="n">
-        <v>7064186</v>
+        <v>7064167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,32 +4992,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427268</v>
+        <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>78801</v>
+        <v>80185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559964</v>
+        <v>560192</v>
       </c>
       <c r="R44" t="n">
-        <v>7064339</v>
+        <v>7064186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427257</v>
+        <v>129427268</v>
       </c>
       <c r="B45" t="n">
-        <v>91843</v>
+        <v>78801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5100,21 +5100,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560200</v>
+        <v>559964</v>
       </c>
       <c r="R45" t="n">
-        <v>7064167</v>
+        <v>7064339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,37 +5186,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129427273</v>
       </c>
       <c r="B46" t="n">
-        <v>57831</v>
+        <v>98716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560001</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064286</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,6 +5269,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5287,10 +5288,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427273</v>
+        <v>129423125</v>
       </c>
       <c r="B47" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5317,19 +5318,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560001</v>
+        <v>560204</v>
       </c>
       <c r="R47" t="n">
-        <v>7064286</v>
+        <v>7064212</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,40 +5360,49 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B48" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,19 +5429,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R48" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,7 +5473,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5473,7 +5483,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5500,49 +5510,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129423615</v>
+        <v>129427266</v>
       </c>
       <c r="B49" t="n">
-        <v>98712</v>
+        <v>57831</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560077</v>
+        <v>560311</v>
       </c>
       <c r="R49" t="n">
-        <v>7064315</v>
+        <v>7064217</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5572,19 +5582,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,57 +5599,61 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129421945</v>
+        <v>129423514</v>
       </c>
       <c r="B50" t="n">
-        <v>92263</v>
+        <v>98716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560235</v>
+        <v>560095</v>
       </c>
       <c r="R50" t="n">
-        <v>7064180</v>
+        <v>7064302</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,7 +5685,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5691,7 +5695,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5721,7 +5725,7 @@
         <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5821,50 +5825,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>92267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R52" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5895,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5905,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5933,49 +5932,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129423514</v>
+        <v>129422827</v>
       </c>
       <c r="B53" t="n">
-        <v>98712</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560095</v>
+        <v>560315</v>
       </c>
       <c r="R53" t="n">
-        <v>7064302</v>
+        <v>7064259</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R6" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,49 +1195,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129424015</v>
+        <v>129422931</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560049</v>
+        <v>560279</v>
       </c>
       <c r="R7" t="n">
-        <v>7064357</v>
+        <v>7064267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1279,7 +1280,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,49 +1312,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427269</v>
+        <v>129427243</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560091</v>
+        <v>560198</v>
       </c>
       <c r="R8" t="n">
-        <v>7064300</v>
+        <v>7064162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1391,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1408,45 +1409,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129427283</v>
+        <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559968</v>
+        <v>560049</v>
       </c>
       <c r="R9" t="n">
-        <v>7064298</v>
+        <v>7064357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,9 +1481,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,62 +1508,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129422931</v>
+        <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560279</v>
+        <v>560091</v>
       </c>
       <c r="R10" t="n">
-        <v>7064267</v>
+        <v>7064300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,44 +1592,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R12" t="n">
         <v>7064186</v>
@@ -1790,6 +1790,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>91969</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,21 +1832,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R13" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,17 +1889,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1918,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129424172</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,34 +1925,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560042</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,19 +1982,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,22 +1999,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427267</v>
+        <v>129424172</v>
       </c>
       <c r="B15" t="n">
-        <v>91968</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,29 +2022,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560309</v>
+        <v>560042</v>
       </c>
       <c r="R15" t="n">
-        <v>7064195</v>
+        <v>7064308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,79 +2079,84 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427271</v>
+        <v>129427256</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560086</v>
+        <v>560241</v>
       </c>
       <c r="R16" t="n">
-        <v>7064325</v>
+        <v>7064201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,7 +2197,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2220,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427282</v>
+        <v>129422438</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,34 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560033</v>
+        <v>560245</v>
       </c>
       <c r="R17" t="n">
-        <v>7064272</v>
+        <v>7064205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,9 +2283,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,57 +2310,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427256</v>
+        <v>129427271</v>
       </c>
       <c r="B18" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560241</v>
+        <v>560086</v>
       </c>
       <c r="R18" t="n">
-        <v>7064201</v>
+        <v>7064325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,6 +2405,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427260</v>
+        <v>129427282</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R19" t="n">
-        <v>7064373</v>
+        <v>7064272</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129422438</v>
+        <v>129427260</v>
       </c>
       <c r="B20" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,34 +2532,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560245</v>
+        <v>559954</v>
       </c>
       <c r="R20" t="n">
-        <v>7064205</v>
+        <v>7064373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2584,19 +2589,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:52</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,57 +2611,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427287</v>
+        <v>129427270</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560090</v>
+        <v>560092</v>
       </c>
       <c r="R21" t="n">
-        <v>7064325</v>
+        <v>7064308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2706,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129419985</v>
+        <v>129427287</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2751,17 +2756,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560212</v>
+        <v>560090</v>
       </c>
       <c r="R22" t="n">
-        <v>7064155</v>
+        <v>7064325</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,19 +2793,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,64 +2810,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R23" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2899,30 +2890,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
         <v>129427254</v>
       </c>
       <c r="B24" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>129424195</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>129427235</v>
       </c>
       <c r="B28" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129422985</v>
+        <v>129420535</v>
       </c>
       <c r="B35" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560263</v>
+        <v>560216</v>
       </c>
       <c r="R35" t="n">
-        <v>7064243</v>
+        <v>7064197</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4162,45 +4162,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427240</v>
+        <v>129424136</v>
       </c>
       <c r="B36" t="n">
-        <v>91513</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560201</v>
+        <v>560048</v>
       </c>
       <c r="R36" t="n">
-        <v>7064160</v>
+        <v>7064312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,9 +4234,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,57 +4261,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427246</v>
+        <v>129422985</v>
       </c>
       <c r="B37" t="n">
-        <v>80178</v>
+        <v>91546</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560192</v>
+        <v>560263</v>
       </c>
       <c r="R37" t="n">
-        <v>7064186</v>
+        <v>7064243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,9 +4341,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4344,57 +4368,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129423749</v>
+        <v>129427240</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>91514</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560086</v>
+        <v>560201</v>
       </c>
       <c r="R38" t="n">
-        <v>7064365</v>
+        <v>7064160</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,19 +4448,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,57 +4465,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129420535</v>
+        <v>129427246</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560216</v>
+        <v>560192</v>
       </c>
       <c r="R39" t="n">
-        <v>7064197</v>
+        <v>7064186</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4531,19 +4545,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,61 +4562,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129424136</v>
+        <v>129423749</v>
       </c>
       <c r="B40" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560048</v>
+        <v>560086</v>
       </c>
       <c r="R40" t="n">
-        <v>7064312</v>
+        <v>7064365</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,32 +4895,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427257</v>
+        <v>129427265</v>
       </c>
       <c r="B43" t="n">
-        <v>91847</v>
+        <v>80185</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560200</v>
+        <v>560192</v>
       </c>
       <c r="R43" t="n">
-        <v>7064167</v>
+        <v>7064186</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,32 +4992,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427265</v>
+        <v>129427268</v>
       </c>
       <c r="B44" t="n">
-        <v>80185</v>
+        <v>78801</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560192</v>
+        <v>559964</v>
       </c>
       <c r="R44" t="n">
-        <v>7064186</v>
+        <v>7064339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,45 +5089,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427268</v>
+        <v>129427266</v>
       </c>
       <c r="B45" t="n">
-        <v>78801</v>
+        <v>57831</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559964</v>
+        <v>560311</v>
       </c>
       <c r="R45" t="n">
-        <v>7064339</v>
+        <v>7064217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,49 +5190,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427273</v>
+        <v>129427257</v>
       </c>
       <c r="B46" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560001</v>
+        <v>560200</v>
       </c>
       <c r="R46" t="n">
-        <v>7064286</v>
+        <v>7064167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,7 +5269,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5288,10 +5287,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129423125</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,19 +5317,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560204</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064212</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5360,49 +5359,40 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423615</v>
+        <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5429,19 +5419,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560077</v>
+        <v>560204</v>
       </c>
       <c r="R48" t="n">
-        <v>7064315</v>
+        <v>7064212</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5473,7 +5463,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5483,7 +5473,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5510,49 +5500,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427266</v>
+        <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>57831</v>
+        <v>98724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560311</v>
+        <v>560077</v>
       </c>
       <c r="R49" t="n">
-        <v>7064217</v>
+        <v>7064315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,9 +5572,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,61 +5599,62 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129423514</v>
+        <v>129422827</v>
       </c>
       <c r="B50" t="n">
-        <v>98716</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560095</v>
+        <v>560315</v>
       </c>
       <c r="R50" t="n">
-        <v>7064302</v>
+        <v>7064259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5685,7 +5686,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5695,7 +5696,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5722,30 +5723,34 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422999</v>
+        <v>129421945</v>
       </c>
       <c r="B51" t="n">
-        <v>91569</v>
+        <v>92268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5753,10 +5758,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560298</v>
+        <v>560235</v>
       </c>
       <c r="R51" t="n">
-        <v>7064242</v>
+        <v>7064180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5798,7 +5803,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5825,34 +5830,30 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B52" t="n">
-        <v>92267</v>
+        <v>91570</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5860,10 +5861,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R52" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5895,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5905,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5932,50 +5933,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129422827</v>
+        <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560315</v>
+        <v>560095</v>
       </c>
       <c r="R53" t="n">
-        <v>7064259</v>
+        <v>7064302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427283</v>
+        <v>129422931</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559968</v>
+        <v>560279</v>
       </c>
       <c r="R6" t="n">
-        <v>7064298</v>
+        <v>7064267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1171,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129422931</v>
+        <v>129427283</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560279</v>
+        <v>559968</v>
       </c>
       <c r="R7" t="n">
-        <v>7064267</v>
+        <v>7064298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,24 +1283,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,12 +1300,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129424015</v>
+        <v>129427269</v>
       </c>
       <c r="B9" t="n">
         <v>98724</v>
@@ -1439,19 +1439,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560049</v>
+        <v>560091</v>
       </c>
       <c r="R9" t="n">
-        <v>7064357</v>
+        <v>7064300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,46 +1481,37 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129427269</v>
+        <v>129424015</v>
       </c>
       <c r="B10" t="n">
         <v>98724</v>
@@ -1550,19 +1541,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560091</v>
+        <v>560049</v>
       </c>
       <c r="R10" t="n">
-        <v>7064300</v>
+        <v>7064357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,30 +1583,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427267</v>
+        <v>129424172</v>
       </c>
       <c r="B13" t="n">
-        <v>91969</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,29 +1832,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560309</v>
+        <v>560042</v>
       </c>
       <c r="R13" t="n">
-        <v>7064195</v>
+        <v>7064308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,30 +1889,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2011,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129424172</v>
+        <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,34 +2036,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560042</v>
+        <v>560309</v>
       </c>
       <c r="R15" t="n">
-        <v>7064308</v>
+        <v>7064195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,49 +2088,40 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427256</v>
+        <v>129427282</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560241</v>
+        <v>560033</v>
       </c>
       <c r="R16" t="n">
-        <v>7064201</v>
+        <v>7064272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,49 +2322,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427271</v>
+        <v>129427260</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560086</v>
+        <v>559954</v>
       </c>
       <c r="R18" t="n">
-        <v>7064325</v>
+        <v>7064373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,13 +2395,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427282</v>
+        <v>129427256</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560033</v>
+        <v>560241</v>
       </c>
       <c r="R19" t="n">
-        <v>7064272</v>
+        <v>7064201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,45 +2521,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R20" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,17 +2598,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2929,45 +2929,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427254</v>
+        <v>129424097</v>
       </c>
       <c r="B24" t="n">
-        <v>92003</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560321</v>
+        <v>560066</v>
       </c>
       <c r="R24" t="n">
-        <v>7064226</v>
+        <v>7064318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,9 +2997,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3014,12 +3024,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3123,45 +3133,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R26" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,19 +3201,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,61 +3218,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129424195</v>
+        <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>96970</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560020</v>
+        <v>560199</v>
       </c>
       <c r="R27" t="n">
-        <v>7064291</v>
+        <v>7064182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3302,19 +3298,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3329,57 +3315,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129427235</v>
+        <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>96970</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560199</v>
+        <v>560020</v>
       </c>
       <c r="R28" t="n">
-        <v>7064182</v>
+        <v>7064291</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3409,9 +3399,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>96970</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>96970</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,57 +4043,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129420535</v>
+        <v>129427240</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560216</v>
+        <v>560201</v>
       </c>
       <c r="R35" t="n">
-        <v>7064197</v>
+        <v>7064160</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,19 +4123,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4150,61 +4140,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129424136</v>
+        <v>129420535</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560048</v>
+        <v>560216</v>
       </c>
       <c r="R36" t="n">
-        <v>7064312</v>
+        <v>7064197</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4236,7 +4222,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4246,7 +4232,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,10 +4366,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427240</v>
+        <v>129427246</v>
       </c>
       <c r="B38" t="n">
-        <v>91514</v>
+        <v>80178</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4391,21 +4377,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4415,10 +4401,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560201</v>
+        <v>560192</v>
       </c>
       <c r="R38" t="n">
-        <v>7064160</v>
+        <v>7064186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4477,45 +4463,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427246</v>
+        <v>129423749</v>
       </c>
       <c r="B39" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560192</v>
+        <v>560086</v>
       </c>
       <c r="R39" t="n">
-        <v>7064186</v>
+        <v>7064365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,9 +4531,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4562,57 +4558,61 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129423749</v>
+        <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560086</v>
+        <v>560048</v>
       </c>
       <c r="R40" t="n">
-        <v>7064365</v>
+        <v>7064312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,32 +4895,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427265</v>
+        <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>80185</v>
+        <v>91848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560192</v>
+        <v>560200</v>
       </c>
       <c r="R43" t="n">
-        <v>7064186</v>
+        <v>7064167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,32 +4992,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427268</v>
+        <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>78801</v>
+        <v>80185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559964</v>
+        <v>560192</v>
       </c>
       <c r="R44" t="n">
-        <v>7064339</v>
+        <v>7064186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,49 +5089,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427266</v>
+        <v>129427268</v>
       </c>
       <c r="B45" t="n">
-        <v>57831</v>
+        <v>78801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560311</v>
+        <v>559964</v>
       </c>
       <c r="R45" t="n">
-        <v>7064217</v>
+        <v>7064339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,45 +5186,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427257</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>91848</v>
+        <v>57831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560200</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064167</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427273</v>
+        <v>129423125</v>
       </c>
       <c r="B47" t="n">
         <v>98724</v>
@@ -5317,19 +5317,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560001</v>
+        <v>560204</v>
       </c>
       <c r="R47" t="n">
-        <v>7064286</v>
+        <v>7064212</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,37 +5359,46 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B48" t="n">
         <v>98724</v>
@@ -5419,19 +5428,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R48" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,7 +5472,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5473,7 +5482,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5500,7 +5509,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129423615</v>
+        <v>129427273</v>
       </c>
       <c r="B49" t="n">
         <v>98724</v>
@@ -5530,19 +5539,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560077</v>
+        <v>560001</v>
       </c>
       <c r="R49" t="n">
-        <v>7064315</v>
+        <v>7064286</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5572,89 +5581,79 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422827</v>
+        <v>129423514</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560315</v>
+        <v>560095</v>
       </c>
       <c r="R50" t="n">
-        <v>7064259</v>
+        <v>7064302</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5685,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5696,7 +5695,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5723,34 +5722,30 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>92268</v>
+        <v>91570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5758,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R51" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5793,7 +5788,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5803,7 +5798,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5830,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422999</v>
+        <v>129422827</v>
       </c>
       <c r="B52" t="n">
-        <v>91570</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5841,30 +5836,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560298</v>
+        <v>560315</v>
       </c>
       <c r="R52" t="n">
-        <v>7064242</v>
+        <v>7064259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5900,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5910,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5933,49 +5937,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129423514</v>
+        <v>129421945</v>
       </c>
       <c r="B53" t="n">
-        <v>98724</v>
+        <v>92268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560095</v>
+        <v>560235</v>
       </c>
       <c r="R53" t="n">
-        <v>7064302</v>
+        <v>7064180</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129422931</v>
+        <v>129427283</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560279</v>
+        <v>559968</v>
       </c>
       <c r="R6" t="n">
-        <v>7064267</v>
+        <v>7064298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,24 +1166,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427283</v>
+        <v>129427243</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559968</v>
+        <v>560198</v>
       </c>
       <c r="R7" t="n">
-        <v>7064298</v>
+        <v>7064162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427243</v>
+        <v>129422931</v>
       </c>
       <c r="B8" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1303,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560198</v>
+        <v>560279</v>
       </c>
       <c r="R8" t="n">
-        <v>7064162</v>
+        <v>7064267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,9 +1365,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427249</v>
+        <v>129424172</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560236</v>
+        <v>560042</v>
       </c>
       <c r="R12" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,14 +1787,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,22 +1814,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129424172</v>
+        <v>129427264</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,34 +1837,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560042</v>
+        <v>560192</v>
       </c>
       <c r="R13" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,19 +1894,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,22 +1911,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,7 +1958,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R14" t="n">
         <v>7064186</v>
@@ -1999,6 +1994,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,45 +2118,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427282</v>
+        <v>129427271</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560033</v>
+        <v>560086</v>
       </c>
       <c r="R16" t="n">
-        <v>7064272</v>
+        <v>7064325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2201,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2215,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129422438</v>
+        <v>129427282</v>
       </c>
       <c r="B17" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,34 +2231,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560245</v>
+        <v>560033</v>
       </c>
       <c r="R17" t="n">
-        <v>7064205</v>
+        <v>7064272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2283,19 +2288,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427260</v>
+        <v>129427256</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559954</v>
+        <v>560241</v>
       </c>
       <c r="R18" t="n">
-        <v>7064373</v>
+        <v>7064201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,11 +2388,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,34 +2425,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R19" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,9 +2482,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,61 +2509,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427271</v>
+        <v>129427260</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560086</v>
+        <v>559954</v>
       </c>
       <c r="R20" t="n">
-        <v>7064325</v>
+        <v>7064373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,13 +2594,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,49 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427270</v>
+        <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560092</v>
+        <v>560090</v>
       </c>
       <c r="R21" t="n">
-        <v>7064308</v>
+        <v>7064325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2725,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427287</v>
+        <v>129419985</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2756,17 +2751,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560090</v>
+        <v>560212</v>
       </c>
       <c r="R22" t="n">
-        <v>7064325</v>
+        <v>7064155</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2793,9 +2788,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,60 +2815,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R23" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2890,84 +2899,75 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R24" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,19 +2997,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,22 +3014,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,34 +3037,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R25" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,9 +3094,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,44 +3121,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B26" t="n">
-        <v>92003</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R26" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>96970</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>96970</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,12 +4043,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4895,45 +4895,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427257</v>
+        <v>129427266</v>
       </c>
       <c r="B43" t="n">
-        <v>91848</v>
+        <v>57831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560200</v>
+        <v>560311</v>
       </c>
       <c r="R43" t="n">
-        <v>7064167</v>
+        <v>7064217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,45 +4996,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427265</v>
+        <v>129427273</v>
       </c>
       <c r="B44" t="n">
-        <v>80185</v>
+        <v>98724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560192</v>
+        <v>560001</v>
       </c>
       <c r="R44" t="n">
-        <v>7064186</v>
+        <v>7064286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5098,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427268</v>
+        <v>129427257</v>
       </c>
       <c r="B45" t="n">
-        <v>78801</v>
+        <v>91848</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5100,21 +5109,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5124,10 +5133,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559964</v>
+        <v>560200</v>
       </c>
       <c r="R45" t="n">
-        <v>7064339</v>
+        <v>7064167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,49 +5195,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129423125</v>
       </c>
       <c r="B46" t="n">
-        <v>57831</v>
+        <v>98724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560204</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064212</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,9 +5267,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5275,19 +5294,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B47" t="n">
         <v>98724</v>
@@ -5317,19 +5336,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R47" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5361,7 +5380,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5371,7 +5390,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5398,49 +5417,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423615</v>
+        <v>129427265</v>
       </c>
       <c r="B48" t="n">
-        <v>98724</v>
+        <v>80185</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560077</v>
+        <v>560192</v>
       </c>
       <c r="R48" t="n">
-        <v>7064315</v>
+        <v>7064186</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5470,19 +5485,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5497,61 +5502,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427273</v>
+        <v>129427268</v>
       </c>
       <c r="B49" t="n">
-        <v>98724</v>
+        <v>78801</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560001</v>
+        <v>559964</v>
       </c>
       <c r="R49" t="n">
-        <v>7064286</v>
+        <v>7064339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5592,7 +5593,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129424010</v>
+        <v>129423507</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>56908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560054</v>
+        <v>560106</v>
       </c>
       <c r="R2" t="n">
-        <v>7064358</v>
+        <v>7064289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129423604</v>
+        <v>129424010</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560085</v>
+        <v>560054</v>
       </c>
       <c r="R3" t="n">
-        <v>7064313</v>
+        <v>7064358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423507</v>
+        <v>129423604</v>
       </c>
       <c r="B4" t="n">
-        <v>56908</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560106</v>
+        <v>560085</v>
       </c>
       <c r="R4" t="n">
-        <v>7064289</v>
+        <v>7064313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1195,45 +1195,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427243</v>
+        <v>129424015</v>
       </c>
       <c r="B7" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560198</v>
+        <v>560049</v>
       </c>
       <c r="R7" t="n">
-        <v>7064162</v>
+        <v>7064357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,9 +1267,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,62 +1294,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129422931</v>
+        <v>129427269</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560279</v>
+        <v>560091</v>
       </c>
       <c r="R8" t="n">
-        <v>7064267</v>
+        <v>7064300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,93 +1378,75 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129427269</v>
+        <v>129427243</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560091</v>
+        <v>560198</v>
       </c>
       <c r="R9" t="n">
-        <v>7064300</v>
+        <v>7064162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1487,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1511,49 +1505,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129424015</v>
+        <v>129422931</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560049</v>
+        <v>560279</v>
       </c>
       <c r="R10" t="n">
-        <v>7064357</v>
+        <v>7064267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1580,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1595,7 +1590,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129424172</v>
+        <v>129427249</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560042</v>
+        <v>560236</v>
       </c>
       <c r="R12" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,19 +1787,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,22 +1809,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427264</v>
+        <v>129427267</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>91972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,21 +1832,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560192</v>
+        <v>560309</v>
       </c>
       <c r="R13" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,6 +1895,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1923,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,7 +1949,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
         <v>7064186</v>
@@ -1994,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427267</v>
+        <v>129424172</v>
       </c>
       <c r="B15" t="n">
-        <v>91969</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,29 +2022,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560309</v>
+        <v>560042</v>
       </c>
       <c r="R15" t="n">
-        <v>7064195</v>
+        <v>7064308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,79 +2079,84 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427271</v>
+        <v>129427256</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>91851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560086</v>
+        <v>560241</v>
       </c>
       <c r="R16" t="n">
-        <v>7064325</v>
+        <v>7064201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,7 +2197,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2220,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427282</v>
+        <v>129422438</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,34 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560033</v>
+        <v>560245</v>
       </c>
       <c r="R17" t="n">
-        <v>7064272</v>
+        <v>7064205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,9 +2283,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,57 +2310,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427256</v>
+        <v>129427271</v>
       </c>
       <c r="B18" t="n">
-        <v>91848</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560241</v>
+        <v>560086</v>
       </c>
       <c r="R18" t="n">
-        <v>7064201</v>
+        <v>7064325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,6 +2405,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129422438</v>
+        <v>129427282</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,34 +2435,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560245</v>
+        <v>560033</v>
       </c>
       <c r="R19" t="n">
-        <v>7064205</v>
+        <v>7064272</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,19 +2492,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,12 +2509,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2623,45 +2623,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427287</v>
+        <v>129427270</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560090</v>
+        <v>560092</v>
       </c>
       <c r="R21" t="n">
-        <v>7064325</v>
+        <v>7064308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2706,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129419985</v>
+        <v>129427287</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2751,17 +2756,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560212</v>
+        <v>560090</v>
       </c>
       <c r="R22" t="n">
-        <v>7064155</v>
+        <v>7064325</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,19 +2793,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,64 +2810,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R23" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2899,62 +2890,71 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B24" t="n">
-        <v>92003</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R24" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427263</v>
+        <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560037</v>
+        <v>560321</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
         <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,45 +4055,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129427240</v>
+        <v>129422985</v>
       </c>
       <c r="B35" t="n">
-        <v>91514</v>
+        <v>91549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560201</v>
+        <v>560263</v>
       </c>
       <c r="R35" t="n">
-        <v>7064160</v>
+        <v>7064243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,9 +4123,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,57 +4150,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129420535</v>
+        <v>129427246</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560216</v>
+        <v>560192</v>
       </c>
       <c r="R36" t="n">
-        <v>7064197</v>
+        <v>7064186</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,19 +4230,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,22 +4247,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129422985</v>
+        <v>129423749</v>
       </c>
       <c r="B37" t="n">
-        <v>91546</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,34 +4270,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560263</v>
+        <v>560086</v>
       </c>
       <c r="R37" t="n">
-        <v>7064243</v>
+        <v>7064365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4366,45 +4366,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427246</v>
+        <v>129420535</v>
       </c>
       <c r="B38" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560192</v>
+        <v>560216</v>
       </c>
       <c r="R38" t="n">
-        <v>7064186</v>
+        <v>7064197</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,9 +4434,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,57 +4461,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129423749</v>
+        <v>129427240</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560086</v>
+        <v>560201</v>
       </c>
       <c r="R39" t="n">
-        <v>7064365</v>
+        <v>7064160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4531,19 +4541,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,12 +4558,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4573,7 +4573,7 @@
         <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,49 +4895,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427266</v>
+        <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>57831</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560311</v>
+        <v>560200</v>
       </c>
       <c r="R43" t="n">
-        <v>7064217</v>
+        <v>7064167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,49 +4992,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427273</v>
+        <v>129427268</v>
       </c>
       <c r="B44" t="n">
-        <v>98724</v>
+        <v>78801</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560001</v>
+        <v>559964</v>
       </c>
       <c r="R44" t="n">
-        <v>7064286</v>
+        <v>7064339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5071,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5098,32 +5089,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427257</v>
+        <v>129427265</v>
       </c>
       <c r="B45" t="n">
-        <v>91848</v>
+        <v>80185</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5133,10 +5124,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560200</v>
+        <v>560192</v>
       </c>
       <c r="R45" t="n">
-        <v>7064167</v>
+        <v>7064186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5195,49 +5186,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129423125</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>98724</v>
+        <v>57831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560204</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064212</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5267,19 +5258,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5294,22 +5275,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129423615</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5336,19 +5317,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560077</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064315</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,84 +5359,79 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427265</v>
+        <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560192</v>
+        <v>560204</v>
       </c>
       <c r="R48" t="n">
-        <v>7064186</v>
+        <v>7064212</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,9 +5461,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5502,57 +5488,61 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427268</v>
+        <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>559964</v>
+        <v>560077</v>
       </c>
       <c r="R49" t="n">
-        <v>7064339</v>
+        <v>7064315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,9 +5572,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,61 +5599,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129423514</v>
+        <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>98724</v>
+        <v>92271</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560095</v>
+        <v>560235</v>
       </c>
       <c r="R50" t="n">
-        <v>7064302</v>
+        <v>7064180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5685,7 +5681,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5695,7 +5691,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5725,7 +5721,7 @@
         <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5825,50 +5821,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422827</v>
+        <v>129423514</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560315</v>
+        <v>560095</v>
       </c>
       <c r="R52" t="n">
-        <v>7064259</v>
+        <v>7064302</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5900,7 +5895,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5910,7 +5905,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5937,45 +5932,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129421945</v>
+        <v>129422827</v>
       </c>
       <c r="B53" t="n">
-        <v>92268</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560235</v>
+        <v>560315</v>
       </c>
       <c r="R53" t="n">
-        <v>7064180</v>
+        <v>7064259</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423507</v>
+        <v>129424010</v>
       </c>
       <c r="B2" t="n">
-        <v>56908</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560106</v>
+        <v>560054</v>
       </c>
       <c r="R2" t="n">
-        <v>7064289</v>
+        <v>7064358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129424010</v>
+        <v>129423604</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560054</v>
+        <v>560085</v>
       </c>
       <c r="R3" t="n">
-        <v>7064358</v>
+        <v>7064313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423604</v>
+        <v>129423507</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>56908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560085</v>
+        <v>560106</v>
       </c>
       <c r="R4" t="n">
-        <v>7064313</v>
+        <v>7064289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427283</v>
+        <v>129422931</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559968</v>
+        <v>560279</v>
       </c>
       <c r="R6" t="n">
-        <v>7064298</v>
+        <v>7064267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1171,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1203,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1505,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129422931</v>
+        <v>129427283</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,39 +1536,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560279</v>
+        <v>559968</v>
       </c>
       <c r="R10" t="n">
-        <v>7064267</v>
+        <v>7064298</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,24 +1593,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,12 +1610,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R12" t="n">
         <v>7064186</v>
@@ -1790,11 +1790,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427267</v>
+        <v>129424172</v>
       </c>
       <c r="B13" t="n">
-        <v>91972</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,29 +1827,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560309</v>
+        <v>560042</v>
       </c>
       <c r="R13" t="n">
-        <v>7064195</v>
+        <v>7064308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,40 +1884,49 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,7 +1958,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R14" t="n">
         <v>7064186</v>
@@ -1985,6 +1994,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129424172</v>
+        <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,34 +2036,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560042</v>
+        <v>560309</v>
       </c>
       <c r="R15" t="n">
-        <v>7064308</v>
+        <v>7064195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,39 +2088,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2322,49 +2322,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427271</v>
+        <v>129427260</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560086</v>
+        <v>559954</v>
       </c>
       <c r="R18" t="n">
-        <v>7064325</v>
+        <v>7064373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,13 +2395,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2521,45 +2521,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R20" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,17 +2598,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,49 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427270</v>
+        <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560092</v>
+        <v>560090</v>
       </c>
       <c r="R21" t="n">
-        <v>7064308</v>
+        <v>7064325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2725,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427287</v>
+        <v>129419985</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2756,17 +2751,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560090</v>
+        <v>560212</v>
       </c>
       <c r="R22" t="n">
-        <v>7064325</v>
+        <v>7064155</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2793,9 +2788,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,60 +2815,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R23" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2890,39 +2899,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>96973</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>96973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,12 +4043,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427246</v>
+        <v>129427240</v>
       </c>
       <c r="B36" t="n">
-        <v>80178</v>
+        <v>91517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4173,21 +4173,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560192</v>
+        <v>560201</v>
       </c>
       <c r="R36" t="n">
-        <v>7064186</v>
+        <v>7064160</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4259,45 +4259,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R37" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,19 +4327,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,22 +4344,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4377,34 +4367,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R38" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,7 +4426,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4446,7 +4436,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4473,45 +4463,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427240</v>
+        <v>129420535</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560201</v>
+        <v>560216</v>
       </c>
       <c r="R39" t="n">
-        <v>7064160</v>
+        <v>7064197</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4541,9 +4531,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,12 +4558,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4895,32 +4895,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427257</v>
+        <v>129427265</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>80185</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560200</v>
+        <v>560192</v>
       </c>
       <c r="R43" t="n">
-        <v>7064167</v>
+        <v>7064186</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427265</v>
+        <v>129427266</v>
       </c>
       <c r="B45" t="n">
-        <v>80185</v>
+        <v>57831</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5100,34 +5100,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560192</v>
+        <v>560311</v>
       </c>
       <c r="R45" t="n">
-        <v>7064186</v>
+        <v>7064217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,37 +5190,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129427273</v>
       </c>
       <c r="B46" t="n">
-        <v>57831</v>
+        <v>98727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5225,10 +5229,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560001</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064286</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,6 +5273,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5287,7 +5292,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427273</v>
+        <v>129423125</v>
       </c>
       <c r="B47" t="n">
         <v>98727</v>
@@ -5317,19 +5322,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560001</v>
+        <v>560204</v>
       </c>
       <c r="R47" t="n">
-        <v>7064286</v>
+        <v>7064212</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,37 +5364,46 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B48" t="n">
         <v>98727</v>
@@ -5419,19 +5433,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R48" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,7 +5477,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5473,7 +5487,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5500,49 +5514,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129423615</v>
+        <v>129427257</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560077</v>
+        <v>560200</v>
       </c>
       <c r="R49" t="n">
-        <v>7064315</v>
+        <v>7064167</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5572,19 +5582,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,46 +5599,42 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B50" t="n">
-        <v>92271</v>
+        <v>91573</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5646,10 +5642,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R50" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,7 +5677,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5691,7 +5687,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5718,41 +5714,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B51" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R51" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,7 +5788,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5794,7 +5798,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5821,49 +5825,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129423514</v>
+        <v>129421945</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560095</v>
+        <v>560235</v>
       </c>
       <c r="R52" t="n">
-        <v>7064302</v>
+        <v>7064180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129422931</v>
+        <v>129427283</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560279</v>
+        <v>559968</v>
       </c>
       <c r="R6" t="n">
-        <v>7064267</v>
+        <v>7064298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,24 +1166,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,61 +1183,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129424015</v>
+        <v>129427243</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560049</v>
+        <v>560198</v>
       </c>
       <c r="R7" t="n">
-        <v>7064357</v>
+        <v>7064162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,19 +1263,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,61 +1280,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427269</v>
+        <v>129422931</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560091</v>
+        <v>560279</v>
       </c>
       <c r="R8" t="n">
-        <v>7064300</v>
+        <v>7064267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,75 +1365,93 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129427243</v>
+        <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560198</v>
+        <v>560049</v>
       </c>
       <c r="R9" t="n">
-        <v>7064162</v>
+        <v>7064357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,9 +1481,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,57 +1508,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129427283</v>
+        <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559968</v>
+        <v>560091</v>
       </c>
       <c r="R10" t="n">
-        <v>7064298</v>
+        <v>7064300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,6 +1603,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R12" t="n">
         <v>7064186</v>
@@ -1790,6 +1790,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,7 +1963,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
         <v>7064186</v>
@@ -1994,11 +1999,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B16" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R16" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,9 +2186,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2203,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,34 +2236,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R17" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2283,19 +2293,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,57 +2310,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R18" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,17 +2399,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2521,49 +2521,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427271</v>
+        <v>129427260</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560086</v>
+        <v>559954</v>
       </c>
       <c r="R20" t="n">
-        <v>7064325</v>
+        <v>7064373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,13 +2594,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2929,32 +2929,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427263</v>
+        <v>129427254</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560037</v>
+        <v>560321</v>
       </c>
       <c r="R24" t="n">
-        <v>7064364</v>
+        <v>7064226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B26" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R26" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R31" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3749,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,21 +3765,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R32" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3820,11 +3825,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>96973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>96973</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,12 +4043,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4162,45 +4162,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427240</v>
+        <v>129420535</v>
       </c>
       <c r="B36" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560201</v>
+        <v>560216</v>
       </c>
       <c r="R36" t="n">
-        <v>7064160</v>
+        <v>7064197</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,9 +4230,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,22 +4257,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427246</v>
+        <v>129427240</v>
       </c>
       <c r="B37" t="n">
-        <v>80178</v>
+        <v>91517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,21 +4280,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4304,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560192</v>
+        <v>560201</v>
       </c>
       <c r="R37" t="n">
-        <v>7064186</v>
+        <v>7064160</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,45 +4366,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R38" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,19 +4434,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,22 +4451,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,34 +4474,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R39" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427265</v>
+        <v>129427266</v>
       </c>
       <c r="B43" t="n">
-        <v>80185</v>
+        <v>57831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4906,34 +4906,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560192</v>
+        <v>560311</v>
       </c>
       <c r="R43" t="n">
-        <v>7064186</v>
+        <v>7064217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,45 +4996,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427268</v>
+        <v>129427273</v>
       </c>
       <c r="B44" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559964</v>
+        <v>560001</v>
       </c>
       <c r="R44" t="n">
-        <v>7064339</v>
+        <v>7064286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5089,49 +5098,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427266</v>
+        <v>129423125</v>
       </c>
       <c r="B45" t="n">
-        <v>57831</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560311</v>
+        <v>560204</v>
       </c>
       <c r="R45" t="n">
-        <v>7064217</v>
+        <v>7064212</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5161,9 +5170,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5178,19 +5197,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427273</v>
+        <v>129423615</v>
       </c>
       <c r="B46" t="n">
         <v>98727</v>
@@ -5220,19 +5239,19 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560001</v>
+        <v>560077</v>
       </c>
       <c r="R46" t="n">
-        <v>7064286</v>
+        <v>7064315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5262,79 +5281,84 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129423125</v>
+        <v>129427268</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560204</v>
+        <v>559964</v>
       </c>
       <c r="R47" t="n">
-        <v>7064212</v>
+        <v>7064339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5364,19 +5388,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,61 +5405,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423615</v>
+        <v>129427257</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560077</v>
+        <v>560200</v>
       </c>
       <c r="R48" t="n">
-        <v>7064315</v>
+        <v>7064167</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5475,19 +5485,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5502,44 +5502,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427257</v>
+        <v>129427265</v>
       </c>
       <c r="B49" t="n">
-        <v>91851</v>
+        <v>80185</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560200</v>
+        <v>560192</v>
       </c>
       <c r="R49" t="n">
-        <v>7064167</v>
+        <v>7064186</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,10 +5611,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422999</v>
+        <v>129422827</v>
       </c>
       <c r="B50" t="n">
-        <v>91573</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,30 +5622,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560298</v>
+        <v>560315</v>
       </c>
       <c r="R50" t="n">
-        <v>7064242</v>
+        <v>7064259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5677,7 +5686,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5687,7 +5696,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5714,49 +5723,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129423514</v>
+        <v>129421945</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560095</v>
+        <v>560235</v>
       </c>
       <c r="R51" t="n">
-        <v>7064302</v>
+        <v>7064180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5798,7 +5803,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5825,34 +5830,30 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B52" t="n">
-        <v>92271</v>
+        <v>91573</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5860,10 +5861,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R52" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5895,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5905,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5932,50 +5933,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129422827</v>
+        <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560315</v>
+        <v>560095</v>
       </c>
       <c r="R53" t="n">
-        <v>7064259</v>
+        <v>7064302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427283</v>
+        <v>129427243</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559968</v>
+        <v>560198</v>
       </c>
       <c r="R6" t="n">
-        <v>7064298</v>
+        <v>7064162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R7" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R12" t="n">
         <v>7064186</v>
@@ -1790,11 +1790,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129424172</v>
+        <v>129427249</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,34 +1827,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560042</v>
+        <v>560236</v>
       </c>
       <c r="R13" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,19 +1884,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,22 +1906,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129424172</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,34 +1929,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560042</v>
       </c>
       <c r="R14" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,9 +1986,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,12 +2013,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R16" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,19 +2186,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B17" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,34 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R17" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,9 +2283,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,61 +2310,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427271</v>
+        <v>129427282</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560086</v>
+        <v>560033</v>
       </c>
       <c r="R18" t="n">
-        <v>7064325</v>
+        <v>7064272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,7 +2401,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2424,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427282</v>
+        <v>129427260</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R19" t="n">
-        <v>7064272</v>
+        <v>7064373</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,45 +2521,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R20" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,17 +2598,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R31" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3723,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,10 +3749,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R32" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,6 +3820,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,45 +4162,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129420535</v>
+        <v>129424136</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560216</v>
+        <v>560048</v>
       </c>
       <c r="R36" t="n">
-        <v>7064197</v>
+        <v>7064312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,7 +4236,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4242,7 +4246,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,45 +4370,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427246</v>
+        <v>129420535</v>
       </c>
       <c r="B38" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560192</v>
+        <v>560216</v>
       </c>
       <c r="R38" t="n">
-        <v>7064186</v>
+        <v>7064197</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,9 +4438,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,57 +4465,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R39" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4531,19 +4545,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,61 +4562,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129424136</v>
+        <v>129423749</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560048</v>
+        <v>560086</v>
       </c>
       <c r="R40" t="n">
-        <v>7064312</v>
+        <v>7064365</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,49 +4895,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427266</v>
+        <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>57831</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560311</v>
+        <v>560200</v>
       </c>
       <c r="R43" t="n">
-        <v>7064217</v>
+        <v>7064167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,49 +4992,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427273</v>
+        <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560001</v>
+        <v>560192</v>
       </c>
       <c r="R44" t="n">
-        <v>7064286</v>
+        <v>7064186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5071,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5098,49 +5089,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129423125</v>
+        <v>129427268</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560204</v>
+        <v>559964</v>
       </c>
       <c r="R45" t="n">
-        <v>7064212</v>
+        <v>7064339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,19 +5157,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5197,61 +5174,61 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129423615</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>57831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560077</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064315</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,19 +5258,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5308,57 +5275,61 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427268</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>559964</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064339</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5399,6 +5370,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5417,45 +5389,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427257</v>
+        <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560200</v>
+        <v>560204</v>
       </c>
       <c r="R48" t="n">
-        <v>7064167</v>
+        <v>7064212</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,9 +5461,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5502,57 +5488,61 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427265</v>
+        <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560192</v>
+        <v>560077</v>
       </c>
       <c r="R49" t="n">
-        <v>7064186</v>
+        <v>7064315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,9 +5572,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,62 +5599,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>92271</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R50" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5681,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5696,7 +5691,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5723,34 +5718,30 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>92271</v>
+        <v>91573</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5758,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R51" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5793,7 +5784,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5803,7 +5794,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5830,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422999</v>
+        <v>129422827</v>
       </c>
       <c r="B52" t="n">
-        <v>91573</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5841,30 +5832,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560298</v>
+        <v>560315</v>
       </c>
       <c r="R52" t="n">
-        <v>7064242</v>
+        <v>7064259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129424010</v>
+        <v>129423604</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560054</v>
+        <v>560085</v>
       </c>
       <c r="R2" t="n">
-        <v>7064358</v>
+        <v>7064313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129423604</v>
+        <v>129424010</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560085</v>
+        <v>560054</v>
       </c>
       <c r="R3" t="n">
-        <v>7064313</v>
+        <v>7064358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R12" t="n">
         <v>7064186</v>
@@ -1790,6 +1790,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,21 +1832,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,7 +1856,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R13" t="n">
         <v>7064186</v>
@@ -1887,11 +1892,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B16" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R16" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,9 +2186,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2203,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,34 +2236,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R17" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2283,19 +2293,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,12 +2310,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427287</v>
+        <v>129419985</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2654,17 +2654,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560090</v>
+        <v>560212</v>
       </c>
       <c r="R21" t="n">
-        <v>7064325</v>
+        <v>7064155</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2691,9 +2691,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2708,19 +2718,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129419985</v>
+        <v>129427287</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2751,17 +2761,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560212</v>
+        <v>560090</v>
       </c>
       <c r="R22" t="n">
-        <v>7064155</v>
+        <v>7064325</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,19 +2798,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,12 +2815,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2929,32 +2929,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B24" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R24" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427263</v>
+        <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560037</v>
+        <v>560321</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4162,49 +4162,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129424136</v>
+        <v>129427240</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560048</v>
+        <v>560201</v>
       </c>
       <c r="R36" t="n">
-        <v>7064312</v>
+        <v>7064160</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4234,19 +4230,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4261,22 +4247,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427240</v>
+        <v>129427246</v>
       </c>
       <c r="B37" t="n">
-        <v>91517</v>
+        <v>80178</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4284,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4308,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560201</v>
+        <v>560192</v>
       </c>
       <c r="R37" t="n">
-        <v>7064160</v>
+        <v>7064186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4370,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4381,34 +4367,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R38" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4440,7 +4426,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4450,7 +4436,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4477,45 +4463,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427246</v>
+        <v>129420535</v>
       </c>
       <c r="B39" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560192</v>
+        <v>560216</v>
       </c>
       <c r="R39" t="n">
-        <v>7064186</v>
+        <v>7064197</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,9 +4531,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4562,57 +4558,61 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129423749</v>
+        <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560086</v>
+        <v>560048</v>
       </c>
       <c r="R40" t="n">
-        <v>7064365</v>
+        <v>7064312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,45 +4895,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427257</v>
+        <v>129427266</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>57831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560200</v>
+        <v>560311</v>
       </c>
       <c r="R43" t="n">
-        <v>7064167</v>
+        <v>7064217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,45 +4996,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427265</v>
+        <v>129427273</v>
       </c>
       <c r="B44" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560192</v>
+        <v>560001</v>
       </c>
       <c r="R44" t="n">
-        <v>7064186</v>
+        <v>7064286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5089,45 +5098,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427268</v>
+        <v>129423125</v>
       </c>
       <c r="B45" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559964</v>
+        <v>560204</v>
       </c>
       <c r="R45" t="n">
-        <v>7064339</v>
+        <v>7064212</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,9 +5170,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5174,61 +5197,61 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129423615</v>
       </c>
       <c r="B46" t="n">
-        <v>57831</v>
+        <v>98727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560077</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,9 +5281,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5275,61 +5308,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427273</v>
+        <v>129427257</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560001</v>
+        <v>560200</v>
       </c>
       <c r="R47" t="n">
-        <v>7064286</v>
+        <v>7064167</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5370,7 +5399,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5389,49 +5417,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423125</v>
+        <v>129427265</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560204</v>
+        <v>560192</v>
       </c>
       <c r="R48" t="n">
-        <v>7064212</v>
+        <v>7064186</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,19 +5485,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,61 +5502,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129423615</v>
+        <v>129427268</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560077</v>
+        <v>559964</v>
       </c>
       <c r="R49" t="n">
-        <v>7064315</v>
+        <v>7064339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5572,19 +5582,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,57 +5599,62 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129421945</v>
+        <v>129422827</v>
       </c>
       <c r="B50" t="n">
-        <v>92271</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560235</v>
+        <v>560315</v>
       </c>
       <c r="R50" t="n">
-        <v>7064180</v>
+        <v>7064259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,7 +5686,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5691,7 +5696,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5718,41 +5723,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B51" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R51" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,7 +5797,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5794,7 +5807,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5821,50 +5834,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>92271</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R52" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5904,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5914,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5933,49 +5941,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129423514</v>
+        <v>129422999</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560095</v>
+        <v>560298</v>
       </c>
       <c r="R53" t="n">
-        <v>7064302</v>
+        <v>7064242</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423604</v>
+        <v>129423507</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>56908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560085</v>
+        <v>560106</v>
       </c>
       <c r="R2" t="n">
-        <v>7064313</v>
+        <v>7064289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423507</v>
+        <v>129423604</v>
       </c>
       <c r="B4" t="n">
-        <v>56908</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560106</v>
+        <v>560085</v>
       </c>
       <c r="R4" t="n">
-        <v>7064289</v>
+        <v>7064313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B6" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R6" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427283</v>
+        <v>129427243</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559968</v>
+        <v>560198</v>
       </c>
       <c r="R7" t="n">
-        <v>7064298</v>
+        <v>7064162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R12" t="n">
         <v>7064186</v>
@@ -1790,11 +1790,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,7 +1851,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R13" t="n">
         <v>7064186</v>
@@ -1892,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,45 +2118,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129422438</v>
+        <v>129427271</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560245</v>
+        <v>560086</v>
       </c>
       <c r="R16" t="n">
-        <v>7064205</v>
+        <v>7064325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,39 +2190,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427282</v>
+        <v>129422438</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,34 +2328,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560033</v>
+        <v>560245</v>
       </c>
       <c r="R18" t="n">
-        <v>7064272</v>
+        <v>7064205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,9 +2385,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,22 +2412,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427260</v>
+        <v>129427282</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R19" t="n">
-        <v>7064373</v>
+        <v>7064272</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,49 +2521,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427271</v>
+        <v>129427260</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560086</v>
+        <v>559954</v>
       </c>
       <c r="R20" t="n">
-        <v>7064325</v>
+        <v>7064373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,13 +2594,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,48 +2623,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R21" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2691,39 +2695,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2827,52 +2822,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R23" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2899,40 +2890,49 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R24" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,9 +2997,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3014,57 +3024,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>92006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R25" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,19 +3104,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,44 +3121,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B26" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R26" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129427242</v>
+        <v>129422764</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,34 +3449,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560320</v>
+        <v>560316</v>
       </c>
       <c r="R29" t="n">
-        <v>7064230</v>
+        <v>7064209</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3506,9 +3511,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,22 +3543,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129422764</v>
+        <v>129427242</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,39 +3566,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560316</v>
+        <v>560320</v>
       </c>
       <c r="R30" t="n">
-        <v>7064209</v>
+        <v>7064230</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3608,24 +3623,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3640,22 +3640,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R31" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3749,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,21 +3765,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R32" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3820,11 +3825,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>96973</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>96973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,12 +4043,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427240</v>
+        <v>129427246</v>
       </c>
       <c r="B36" t="n">
-        <v>91517</v>
+        <v>80178</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4173,21 +4173,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560201</v>
+        <v>560192</v>
       </c>
       <c r="R36" t="n">
-        <v>7064160</v>
+        <v>7064186</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4259,45 +4259,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427246</v>
+        <v>129423749</v>
       </c>
       <c r="B37" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560192</v>
+        <v>560086</v>
       </c>
       <c r="R37" t="n">
-        <v>7064186</v>
+        <v>7064365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,9 +4327,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4344,57 +4354,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129423749</v>
+        <v>129427240</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>91517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560086</v>
+        <v>560201</v>
       </c>
       <c r="R38" t="n">
-        <v>7064365</v>
+        <v>7064160</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,19 +4434,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,12 +4451,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4895,49 +4895,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427266</v>
+        <v>129427268</v>
       </c>
       <c r="B43" t="n">
-        <v>57831</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560311</v>
+        <v>559964</v>
       </c>
       <c r="R43" t="n">
-        <v>7064217</v>
+        <v>7064339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,49 +4992,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427273</v>
+        <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560001</v>
+        <v>560192</v>
       </c>
       <c r="R44" t="n">
-        <v>7064286</v>
+        <v>7064186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5071,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5098,7 +5089,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B45" t="n">
         <v>98727</v>
@@ -5128,19 +5119,19 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R45" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,7 +5163,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5182,7 +5173,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5209,49 +5200,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129423615</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>57831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560077</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064315</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,19 +5272,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5308,12 +5289,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5417,45 +5398,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427265</v>
+        <v>129427273</v>
       </c>
       <c r="B48" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560192</v>
+        <v>560001</v>
       </c>
       <c r="R48" t="n">
-        <v>7064186</v>
+        <v>7064286</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5496,6 +5481,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5514,45 +5500,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427268</v>
+        <v>129423125</v>
       </c>
       <c r="B49" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>559964</v>
+        <v>560204</v>
       </c>
       <c r="R49" t="n">
-        <v>7064339</v>
+        <v>7064212</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,9 +5572,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,62 +5599,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>92271</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R50" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5681,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5696,7 +5691,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5834,45 +5829,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129421945</v>
+        <v>129422827</v>
       </c>
       <c r="B52" t="n">
-        <v>92271</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560235</v>
+        <v>560315</v>
       </c>
       <c r="R52" t="n">
-        <v>7064180</v>
+        <v>7064259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423507</v>
+        <v>129423604</v>
       </c>
       <c r="B2" t="n">
-        <v>56908</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560106</v>
+        <v>560085</v>
       </c>
       <c r="R2" t="n">
-        <v>7064289</v>
+        <v>7064313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129424010</v>
+        <v>129423507</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>56911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560054</v>
+        <v>560106</v>
       </c>
       <c r="R3" t="n">
-        <v>7064358</v>
+        <v>7064289</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423604</v>
+        <v>129424010</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560085</v>
+        <v>560054</v>
       </c>
       <c r="R4" t="n">
-        <v>7064313</v>
+        <v>7064358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>129427285</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427283</v>
+        <v>129427243</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559968</v>
+        <v>560198</v>
       </c>
       <c r="R6" t="n">
-        <v>7064298</v>
+        <v>7064162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R7" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>129422931</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>129427286</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>129427264</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>129427249</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>129424172</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>91972</v>
+        <v>92000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,49 +2118,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427271</v>
+        <v>129427260</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560086</v>
+        <v>559954</v>
       </c>
       <c r="R16" t="n">
-        <v>7064325</v>
+        <v>7064373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,13 +2191,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427256</v>
+        <v>129427282</v>
       </c>
       <c r="B17" t="n">
-        <v>91851</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560241</v>
+        <v>560033</v>
       </c>
       <c r="R17" t="n">
-        <v>7064201</v>
+        <v>7064272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,34 +2328,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R18" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,19 +2385,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,22 +2402,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427282</v>
+        <v>129422438</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,34 +2425,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560033</v>
+        <v>560245</v>
       </c>
       <c r="R19" t="n">
-        <v>7064272</v>
+        <v>7064205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,9 +2482,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,57 +2509,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R20" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,17 +2598,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>129427270</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>129427287</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,45 +2929,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>92034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R24" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,19 +2997,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,44 +3014,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B25" t="n">
-        <v>92006</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R25" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,34 +3134,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,9 +3191,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
         <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129422764</v>
+        <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,39 +3449,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560316</v>
+        <v>560320</v>
       </c>
       <c r="R29" t="n">
-        <v>7064209</v>
+        <v>7064230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3511,24 +3506,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3543,22 +3523,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129427242</v>
+        <v>129422764</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,34 +3546,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560320</v>
+        <v>560316</v>
       </c>
       <c r="R30" t="n">
-        <v>7064230</v>
+        <v>7064209</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3623,9 +3608,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3640,22 +3640,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R31" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3723,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,10 +3749,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R32" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,6 +3820,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3854,7 +3854,7 @@
         <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,45 +4055,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129422985</v>
+        <v>129427240</v>
       </c>
       <c r="B35" t="n">
-        <v>91549</v>
+        <v>91545</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560263</v>
+        <v>560201</v>
       </c>
       <c r="R35" t="n">
-        <v>7064243</v>
+        <v>7064160</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,19 +4123,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4150,12 +4140,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4165,7 +4155,7 @@
         <v>129427246</v>
       </c>
       <c r="B36" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4262,7 +4252,7 @@
         <v>129423749</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,45 +4356,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427240</v>
+        <v>129420535</v>
       </c>
       <c r="B38" t="n">
-        <v>91517</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560201</v>
+        <v>560216</v>
       </c>
       <c r="R38" t="n">
-        <v>7064160</v>
+        <v>7064197</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,9 +4424,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,22 +4451,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129420535</v>
+        <v>129422985</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>91577</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560216</v>
+        <v>560263</v>
       </c>
       <c r="R39" t="n">
-        <v>7064197</v>
+        <v>7064243</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4573,7 +4573,7 @@
         <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>129427288</v>
       </c>
       <c r="B41" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>129424292</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427268</v>
+        <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>91879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4906,21 +4906,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>559964</v>
+        <v>560200</v>
       </c>
       <c r="R43" t="n">
-        <v>7064339</v>
+        <v>7064167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4995,7 +4995,7 @@
         <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5089,49 +5089,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129423615</v>
+        <v>129427268</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>78827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560077</v>
+        <v>559964</v>
       </c>
       <c r="R45" t="n">
-        <v>7064315</v>
+        <v>7064339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5161,19 +5157,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5188,12 +5174,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5203,7 +5189,7 @@
         <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5301,45 +5287,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427257</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>91851</v>
+        <v>98756</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560200</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064167</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,6 +5370,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5398,10 +5389,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427273</v>
+        <v>129423615</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5428,19 +5419,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560001</v>
+        <v>560077</v>
       </c>
       <c r="R48" t="n">
-        <v>7064286</v>
+        <v>7064315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5470,30 +5461,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5503,7 +5503,7 @@
         <v>129423125</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5718,49 +5718,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129423514</v>
+        <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>91601</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560095</v>
+        <v>560298</v>
       </c>
       <c r="R51" t="n">
-        <v>7064302</v>
+        <v>7064242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5792,7 +5784,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5802,7 +5794,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5832,7 +5824,7 @@
         <v>129422827</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5941,41 +5933,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>91573</v>
+        <v>98756</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R53" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423604</v>
+        <v>129424010</v>
       </c>
       <c r="B2" t="n">
         <v>79070</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560085</v>
+        <v>560054</v>
       </c>
       <c r="R2" t="n">
-        <v>7064313</v>
+        <v>7064358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129423507</v>
+        <v>129423604</v>
       </c>
       <c r="B3" t="n">
-        <v>56911</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560106</v>
+        <v>560085</v>
       </c>
       <c r="R3" t="n">
-        <v>7064289</v>
+        <v>7064313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129424010</v>
+        <v>129423507</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>56911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560054</v>
+        <v>560106</v>
       </c>
       <c r="R4" t="n">
-        <v>7064358</v>
+        <v>7064289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B6" t="n">
-        <v>91581</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R6" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427283</v>
+        <v>129422931</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,34 +1206,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559968</v>
+        <v>560279</v>
       </c>
       <c r="R7" t="n">
-        <v>7064298</v>
+        <v>7064267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,9 +1268,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,22 +1300,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129422931</v>
+        <v>129427243</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>91581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560279</v>
+        <v>560198</v>
       </c>
       <c r="R8" t="n">
-        <v>7064267</v>
+        <v>7064162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,24 +1380,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427260</v>
+        <v>129427282</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R16" t="n">
-        <v>7064373</v>
+        <v>7064272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427282</v>
+        <v>129427256</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>91879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560033</v>
+        <v>560241</v>
       </c>
       <c r="R17" t="n">
-        <v>7064272</v>
+        <v>7064201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B18" t="n">
-        <v>91879</v>
+        <v>91581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,34 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R18" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,9 +2380,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,22 +2407,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129422438</v>
+        <v>129427260</v>
       </c>
       <c r="B19" t="n">
-        <v>91581</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,34 +2430,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560245</v>
+        <v>559954</v>
       </c>
       <c r="R19" t="n">
-        <v>7064205</v>
+        <v>7064373</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,19 +2487,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,12 +2509,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>97002</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>97002</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,57 +4043,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129427240</v>
+        <v>129422985</v>
       </c>
       <c r="B35" t="n">
-        <v>91545</v>
+        <v>91577</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560201</v>
+        <v>560263</v>
       </c>
       <c r="R35" t="n">
-        <v>7064160</v>
+        <v>7064243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,9 +4123,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,22 +4150,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427246</v>
+        <v>129427240</v>
       </c>
       <c r="B36" t="n">
-        <v>80204</v>
+        <v>91545</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,21 +4173,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4187,10 +4197,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560192</v>
+        <v>560201</v>
       </c>
       <c r="R36" t="n">
-        <v>7064186</v>
+        <v>7064160</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4249,45 +4259,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B37" t="n">
-        <v>80175</v>
+        <v>80204</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R37" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,19 +4327,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4344,22 +4344,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,34 +4367,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R38" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4463,10 +4463,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129422985</v>
+        <v>129420535</v>
       </c>
       <c r="B39" t="n">
-        <v>91577</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560263</v>
+        <v>560216</v>
       </c>
       <c r="R39" t="n">
-        <v>7064243</v>
+        <v>7064197</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5611,45 +5611,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129421945</v>
+        <v>129422827</v>
       </c>
       <c r="B50" t="n">
-        <v>92299</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560235</v>
+        <v>560315</v>
       </c>
       <c r="R50" t="n">
-        <v>7064180</v>
+        <v>7064259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,7 +5686,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5691,7 +5696,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5821,50 +5826,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>92299</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R52" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129424010</v>
+        <v>129423507</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>56916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560054</v>
+        <v>560106</v>
       </c>
       <c r="R2" t="n">
-        <v>7064358</v>
+        <v>7064289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129423604</v>
+        <v>129424010</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560085</v>
+        <v>560054</v>
       </c>
       <c r="R3" t="n">
-        <v>7064313</v>
+        <v>7064358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423507</v>
+        <v>129423604</v>
       </c>
       <c r="B4" t="n">
-        <v>56911</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560106</v>
+        <v>560085</v>
       </c>
       <c r="R4" t="n">
-        <v>7064289</v>
+        <v>7064313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>129427285</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,45 +1098,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427283</v>
+        <v>129424015</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559968</v>
+        <v>560049</v>
       </c>
       <c r="R6" t="n">
-        <v>7064298</v>
+        <v>7064357</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1170,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,62 +1197,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129422931</v>
+        <v>129427269</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560279</v>
+        <v>560091</v>
       </c>
       <c r="R7" t="n">
-        <v>7064267</v>
+        <v>7064300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,44 +1281,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1315,7 +1314,7 @@
         <v>129427243</v>
       </c>
       <c r="B8" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,49 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129424015</v>
+        <v>129427283</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560049</v>
+        <v>559968</v>
       </c>
       <c r="R9" t="n">
-        <v>7064357</v>
+        <v>7064298</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,19 +1476,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,61 +1493,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129427269</v>
+        <v>129422931</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560091</v>
+        <v>560279</v>
       </c>
       <c r="R10" t="n">
-        <v>7064300</v>
+        <v>7064267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,30 +1578,44 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
         <v>129427286</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427264</v>
+        <v>129427267</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>92006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560192</v>
+        <v>560309</v>
       </c>
       <c r="R12" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,6 +1793,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1816,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427249</v>
+        <v>129424172</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,34 +1823,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560236</v>
+        <v>560042</v>
       </c>
       <c r="R13" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,14 +1880,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,22 +1907,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129424172</v>
+        <v>129427249</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,34 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560042</v>
+        <v>560236</v>
       </c>
       <c r="R14" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,19 +1987,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427267</v>
+        <v>129427264</v>
       </c>
       <c r="B15" t="n">
-        <v>92000</v>
+        <v>80180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,16 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560309</v>
+        <v>560192</v>
       </c>
       <c r="R15" t="n">
-        <v>7064195</v>
+        <v>7064186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,7 +2100,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2118,45 +2118,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427282</v>
+        <v>129427271</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560033</v>
+        <v>560086</v>
       </c>
       <c r="R16" t="n">
-        <v>7064272</v>
+        <v>7064325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,6 +2201,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2215,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427256</v>
+        <v>129427260</v>
       </c>
       <c r="B17" t="n">
-        <v>91879</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560241</v>
+        <v>559954</v>
       </c>
       <c r="R17" t="n">
-        <v>7064201</v>
+        <v>7064373</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B18" t="n">
-        <v>91581</v>
+        <v>91885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R18" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,19 +2390,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,22 +2407,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427260</v>
+        <v>129422438</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,34 +2430,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559954</v>
+        <v>560245</v>
       </c>
       <c r="R19" t="n">
-        <v>7064373</v>
+        <v>7064205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,14 +2487,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,61 +2514,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427271</v>
+        <v>129427282</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560086</v>
+        <v>560033</v>
       </c>
       <c r="R20" t="n">
-        <v>7064325</v>
+        <v>7064272</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,7 +2605,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,49 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427270</v>
+        <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560092</v>
+        <v>560090</v>
       </c>
       <c r="R21" t="n">
-        <v>7064308</v>
+        <v>7064325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2725,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427287</v>
+        <v>129419985</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,17 +2751,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560090</v>
+        <v>560212</v>
       </c>
       <c r="R22" t="n">
-        <v>7064325</v>
+        <v>7064155</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2793,9 +2788,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,60 +2815,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R23" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2890,84 +2899,75 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427254</v>
+        <v>129424097</v>
       </c>
       <c r="B24" t="n">
-        <v>92034</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560321</v>
+        <v>560066</v>
       </c>
       <c r="R24" t="n">
-        <v>7064226</v>
+        <v>7064318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,9 +2997,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3014,12 +3024,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3029,7 +3039,7 @@
         <v>129427263</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,45 +3133,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>92040</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R26" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,19 +3201,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
         <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129427242</v>
+        <v>129422764</v>
       </c>
       <c r="B29" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,34 +3449,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560320</v>
+        <v>560316</v>
       </c>
       <c r="R29" t="n">
-        <v>7064230</v>
+        <v>7064209</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3506,9 +3511,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,22 +3543,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129422764</v>
+        <v>129427242</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,39 +3566,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560316</v>
+        <v>560320</v>
       </c>
       <c r="R30" t="n">
-        <v>7064209</v>
+        <v>7064230</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3608,24 +3623,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3640,12 +3640,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
         <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>129427250</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,45 +4055,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129422985</v>
+        <v>129424136</v>
       </c>
       <c r="B35" t="n">
-        <v>91577</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560263</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7064243</v>
+        <v>7064312</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,7 +4129,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4135,7 +4139,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4165,7 +4169,7 @@
         <v>129427240</v>
       </c>
       <c r="B36" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4259,45 +4263,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427246</v>
+        <v>129423749</v>
       </c>
       <c r="B37" t="n">
-        <v>80204</v>
+        <v>80180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560192</v>
+        <v>560086</v>
       </c>
       <c r="R37" t="n">
-        <v>7064186</v>
+        <v>7064365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,9 +4331,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4344,22 +4358,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129423749</v>
+        <v>129422985</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>91583</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,34 +4381,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560086</v>
+        <v>560263</v>
       </c>
       <c r="R38" t="n">
-        <v>7064365</v>
+        <v>7064243</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,7 +4440,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4436,7 +4450,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4466,7 +4480,7 @@
         <v>129420535</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,49 +4584,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129424136</v>
+        <v>129427246</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>80209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560048</v>
+        <v>560192</v>
       </c>
       <c r="R40" t="n">
-        <v>7064312</v>
+        <v>7064186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4642,19 +4652,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,12 +4669,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4684,7 +4684,7 @@
         <v>129427288</v>
       </c>
       <c r="B41" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>129424292</v>
       </c>
       <c r="B42" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,32 +4992,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427265</v>
+        <v>129427268</v>
       </c>
       <c r="B44" t="n">
-        <v>80211</v>
+        <v>78832</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560192</v>
+        <v>559964</v>
       </c>
       <c r="R44" t="n">
-        <v>7064186</v>
+        <v>7064339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,45 +5089,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427268</v>
+        <v>129427266</v>
       </c>
       <c r="B45" t="n">
-        <v>78827</v>
+        <v>57839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559964</v>
+        <v>560311</v>
       </c>
       <c r="R45" t="n">
-        <v>7064339</v>
+        <v>7064217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,10 +5190,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129427265</v>
       </c>
       <c r="B46" t="n">
-        <v>57834</v>
+        <v>80216</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5197,38 +5201,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560192</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064186</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
         <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5389,10 +5389,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423615</v>
+        <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,19 +5419,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560077</v>
+        <v>560204</v>
       </c>
       <c r="R48" t="n">
-        <v>7064315</v>
+        <v>7064212</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5500,10 +5500,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5530,19 +5530,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R49" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5611,10 +5611,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422827</v>
+        <v>129422999</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>91607</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,39 +5622,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560315</v>
+        <v>560298</v>
       </c>
       <c r="R50" t="n">
-        <v>7064259</v>
+        <v>7064242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5677,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5696,7 +5687,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5723,41 +5714,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B51" t="n">
-        <v>91601</v>
+        <v>98768</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R51" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5789,7 +5788,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5799,7 +5798,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5829,7 +5828,7 @@
         <v>129421945</v>
       </c>
       <c r="B52" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5933,49 +5932,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129423514</v>
+        <v>129422827</v>
       </c>
       <c r="B53" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560095</v>
+        <v>560315</v>
       </c>
       <c r="R53" t="n">
-        <v>7064302</v>
+        <v>7064259</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423507</v>
+        <v>129424010</v>
       </c>
       <c r="B2" t="n">
-        <v>56916</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560106</v>
+        <v>560054</v>
       </c>
       <c r="R2" t="n">
-        <v>7064289</v>
+        <v>7064358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129424010</v>
+        <v>129423604</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560054</v>
+        <v>560085</v>
       </c>
       <c r="R3" t="n">
-        <v>7064358</v>
+        <v>7064313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423604</v>
+        <v>129423507</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560085</v>
+        <v>560106</v>
       </c>
       <c r="R4" t="n">
-        <v>7064313</v>
+        <v>7064289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>129427285</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,49 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129424015</v>
+        <v>129427283</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560049</v>
+        <v>559968</v>
       </c>
       <c r="R6" t="n">
-        <v>7064357</v>
+        <v>7064298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,19 +1166,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,61 +1183,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427269</v>
+        <v>129427243</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560091</v>
+        <v>560198</v>
       </c>
       <c r="R7" t="n">
-        <v>7064300</v>
+        <v>7064162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1274,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427243</v>
+        <v>129422931</v>
       </c>
       <c r="B8" t="n">
-        <v>91587</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,34 +1303,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560198</v>
+        <v>560279</v>
       </c>
       <c r="R8" t="n">
-        <v>7064162</v>
+        <v>7064267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,9 +1365,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,57 +1397,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129427283</v>
+        <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559968</v>
+        <v>560049</v>
       </c>
       <c r="R9" t="n">
-        <v>7064298</v>
+        <v>7064357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,9 +1481,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,62 +1508,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129422931</v>
+        <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560279</v>
+        <v>560091</v>
       </c>
       <c r="R10" t="n">
-        <v>7064267</v>
+        <v>7064300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,44 +1592,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
         <v>129427286</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427267</v>
+        <v>129427249</v>
       </c>
       <c r="B12" t="n">
-        <v>92006</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,16 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560309</v>
+        <v>560236</v>
       </c>
       <c r="R12" t="n">
-        <v>7064195</v>
+        <v>7064186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,13 +1792,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1815,7 +1824,7 @@
         <v>129424172</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>57732</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,7 +1963,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
         <v>7064186</v>
@@ -1990,11 +1999,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427264</v>
+        <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>80180</v>
+        <v>92007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2036,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560192</v>
+        <v>560309</v>
       </c>
       <c r="R15" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,6 +2099,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2118,49 +2118,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427271</v>
+        <v>129427256</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>91886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560086</v>
+        <v>560241</v>
       </c>
       <c r="R16" t="n">
-        <v>7064325</v>
+        <v>7064201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,7 +2197,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2220,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427260</v>
+        <v>129427282</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R17" t="n">
-        <v>7064373</v>
+        <v>7064272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,45 +2312,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427256</v>
+        <v>129427271</v>
       </c>
       <c r="B18" t="n">
-        <v>91885</v>
+        <v>98769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560241</v>
+        <v>560086</v>
       </c>
       <c r="R18" t="n">
-        <v>7064201</v>
+        <v>7064325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,6 +2395,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2422,7 +2417,7 @@
         <v>129422438</v>
       </c>
       <c r="B19" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427282</v>
+        <v>129427260</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R20" t="n">
-        <v>7064272</v>
+        <v>7064373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,6 +2592,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,45 +2623,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427287</v>
+        <v>129427270</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560090</v>
+        <v>560092</v>
       </c>
       <c r="R21" t="n">
-        <v>7064325</v>
+        <v>7064308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2706,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129419985</v>
+        <v>129427287</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,17 +2756,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560212</v>
+        <v>560090</v>
       </c>
       <c r="R22" t="n">
-        <v>7064155</v>
+        <v>7064325</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,19 +2793,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,64 +2810,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R23" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2899,30 +2890,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
         <v>129424097</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427263</v>
+        <v>129427254</v>
       </c>
       <c r="B25" t="n">
-        <v>80180</v>
+        <v>92041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560037</v>
+        <v>560321</v>
       </c>
       <c r="R25" t="n">
-        <v>7064364</v>
+        <v>7064226</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B26" t="n">
-        <v>92040</v>
+        <v>80181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R26" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
         <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129422764</v>
+        <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,39 +3449,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560316</v>
+        <v>560320</v>
       </c>
       <c r="R29" t="n">
-        <v>7064209</v>
+        <v>7064230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3511,24 +3506,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3543,22 +3523,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129427242</v>
+        <v>129422764</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,34 +3546,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560320</v>
+        <v>560316</v>
       </c>
       <c r="R30" t="n">
-        <v>7064230</v>
+        <v>7064209</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3623,9 +3608,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3640,22 +3640,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R31" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3749,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B32" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,21 +3765,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R32" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3820,11 +3825,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>97014</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>97015</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,61 +4043,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129424136</v>
+        <v>129427240</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>91552</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560201</v>
       </c>
       <c r="R35" t="n">
-        <v>7064312</v>
+        <v>7064160</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4127,19 +4123,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4154,57 +4140,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427240</v>
+        <v>129420535</v>
       </c>
       <c r="B36" t="n">
-        <v>91551</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560201</v>
+        <v>560216</v>
       </c>
       <c r="R36" t="n">
-        <v>7064160</v>
+        <v>7064197</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4234,9 +4220,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,22 +4247,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129423749</v>
+        <v>129422985</v>
       </c>
       <c r="B37" t="n">
-        <v>80180</v>
+        <v>91584</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,34 +4270,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560086</v>
+        <v>560263</v>
       </c>
       <c r="R37" t="n">
-        <v>7064365</v>
+        <v>7064243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4333,7 +4329,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4343,7 +4339,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4370,45 +4366,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129422985</v>
+        <v>129427246</v>
       </c>
       <c r="B38" t="n">
-        <v>91583</v>
+        <v>80210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560263</v>
+        <v>560192</v>
       </c>
       <c r="R38" t="n">
-        <v>7064243</v>
+        <v>7064186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4438,19 +4434,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4465,22 +4451,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4488,34 +4474,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R39" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,7 +4533,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4557,7 +4543,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,45 +4570,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129427246</v>
+        <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>80209</v>
+        <v>98769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560192</v>
+        <v>560048</v>
       </c>
       <c r="R40" t="n">
-        <v>7064186</v>
+        <v>7064312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,9 +4642,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,12 +4669,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4684,7 +4684,7 @@
         <v>129427288</v>
       </c>
       <c r="B41" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>129424292</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4992,32 +4992,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427268</v>
+        <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>78832</v>
+        <v>80217</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>559964</v>
+        <v>560192</v>
       </c>
       <c r="R44" t="n">
-        <v>7064339</v>
+        <v>7064186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,49 +5089,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427266</v>
+        <v>129427268</v>
       </c>
       <c r="B45" t="n">
-        <v>57839</v>
+        <v>78833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560311</v>
+        <v>559964</v>
       </c>
       <c r="R45" t="n">
-        <v>7064217</v>
+        <v>7064339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,10 +5186,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427265</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>80216</v>
+        <v>57840</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5201,34 +5197,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560192</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064186</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
         <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5611,10 +5611,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422999</v>
+        <v>129422827</v>
       </c>
       <c r="B50" t="n">
-        <v>91607</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,30 +5622,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560298</v>
+        <v>560315</v>
       </c>
       <c r="R50" t="n">
-        <v>7064242</v>
+        <v>7064259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5677,7 +5686,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5687,7 +5696,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5717,7 +5726,7 @@
         <v>129423514</v>
       </c>
       <c r="B51" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5828,7 +5837,7 @@
         <v>129421945</v>
       </c>
       <c r="B52" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5932,10 +5941,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129422827</v>
+        <v>129422999</v>
       </c>
       <c r="B53" t="n">
-        <v>57732</v>
+        <v>91608</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5943,39 +5952,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560315</v>
+        <v>560298</v>
       </c>
       <c r="R53" t="n">
-        <v>7064259</v>
+        <v>7064242</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129424010</v>
+        <v>129423507</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560054</v>
+        <v>560106</v>
       </c>
       <c r="R2" t="n">
-        <v>7064358</v>
+        <v>7064289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129423604</v>
+        <v>129424010</v>
       </c>
       <c r="B3" t="n">
         <v>79076</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560085</v>
+        <v>560054</v>
       </c>
       <c r="R3" t="n">
-        <v>7064313</v>
+        <v>7064358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423507</v>
+        <v>129423604</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560106</v>
+        <v>560085</v>
       </c>
       <c r="R4" t="n">
-        <v>7064289</v>
+        <v>7064313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427282</v>
+        <v>129427260</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R17" t="n">
-        <v>7064272</v>
+        <v>7064373</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,49 +2317,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427271</v>
+        <v>129427282</v>
       </c>
       <c r="B18" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560086</v>
+        <v>560033</v>
       </c>
       <c r="R18" t="n">
-        <v>7064325</v>
+        <v>7064272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,7 +2396,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2521,45 +2521,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R20" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,17 +2598,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,49 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427270</v>
+        <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560092</v>
+        <v>560090</v>
       </c>
       <c r="R21" t="n">
-        <v>7064308</v>
+        <v>7064325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2725,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427287</v>
+        <v>129419985</v>
       </c>
       <c r="B22" t="n">
         <v>79076</v>
@@ -2756,17 +2751,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560090</v>
+        <v>560212</v>
       </c>
       <c r="R22" t="n">
-        <v>7064325</v>
+        <v>7064155</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2793,9 +2788,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,60 +2815,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R23" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2890,39 +2899,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R31" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3723,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,10 +3749,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R32" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,6 +3820,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>97015</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>97015</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,12 +4043,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5186,37 +5186,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129427273</v>
       </c>
       <c r="B46" t="n">
-        <v>57840</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560001</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064286</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,6 +5269,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5287,7 +5288,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427273</v>
+        <v>129423125</v>
       </c>
       <c r="B47" t="n">
         <v>98769</v>
@@ -5317,19 +5318,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560001</v>
+        <v>560204</v>
       </c>
       <c r="R47" t="n">
-        <v>7064286</v>
+        <v>7064212</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,37 +5360,46 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423125</v>
+        <v>129423615</v>
       </c>
       <c r="B48" t="n">
         <v>98769</v>
@@ -5419,19 +5429,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560204</v>
+        <v>560077</v>
       </c>
       <c r="R48" t="n">
-        <v>7064212</v>
+        <v>7064315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,7 +5473,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5473,7 +5483,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5500,49 +5510,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129423615</v>
+        <v>129427266</v>
       </c>
       <c r="B49" t="n">
-        <v>98769</v>
+        <v>57840</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560077</v>
+        <v>560311</v>
       </c>
       <c r="R49" t="n">
-        <v>7064315</v>
+        <v>7064217</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5572,19 +5582,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,62 +5599,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>92306</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R50" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5681,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5696,7 +5691,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5723,49 +5718,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129423514</v>
+        <v>129422827</v>
       </c>
       <c r="B51" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560095</v>
+        <v>560315</v>
       </c>
       <c r="R51" t="n">
-        <v>7064302</v>
+        <v>7064259</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5797,7 +5793,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5807,7 +5803,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5834,34 +5830,30 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B52" t="n">
-        <v>92306</v>
+        <v>91608</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5869,10 +5861,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R52" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5904,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5914,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5941,41 +5933,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>91608</v>
+        <v>98769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R53" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423507</v>
+        <v>129424010</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560106</v>
+        <v>560054</v>
       </c>
       <c r="R2" t="n">
-        <v>7064289</v>
+        <v>7064358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129424010</v>
+        <v>129423604</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560054</v>
+        <v>560085</v>
       </c>
       <c r="R3" t="n">
-        <v>7064358</v>
+        <v>7064313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423604</v>
+        <v>129423507</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560085</v>
+        <v>560106</v>
       </c>
       <c r="R4" t="n">
-        <v>7064313</v>
+        <v>7064289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>129427285</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427283</v>
+        <v>129427243</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559968</v>
+        <v>560198</v>
       </c>
       <c r="R6" t="n">
-        <v>7064298</v>
+        <v>7064162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R7" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,7 +1412,7 @@
         <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>129427286</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>92012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R12" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,17 +1787,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129424172</v>
+        <v>129427249</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,34 +1823,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560042</v>
+        <v>560236</v>
       </c>
       <c r="R13" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,19 +1880,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,12 +1902,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1931,7 +1917,7 @@
         <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427267</v>
+        <v>129424172</v>
       </c>
       <c r="B15" t="n">
-        <v>92007</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,29 +2022,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560309</v>
+        <v>560042</v>
       </c>
       <c r="R15" t="n">
-        <v>7064195</v>
+        <v>7064308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,40 +2079,49 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B16" t="n">
-        <v>91886</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R16" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,9 +2186,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2203,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427260</v>
+        <v>129427282</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R17" t="n">
-        <v>7064373</v>
+        <v>7064272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427282</v>
+        <v>129427260</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R18" t="n">
-        <v>7064272</v>
+        <v>7064373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,6 +2393,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B19" t="n">
-        <v>91588</v>
+        <v>91891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,34 +2435,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R19" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,19 +2492,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,12 +2509,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
         <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129419985</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,45 +2929,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129424097</v>
+        <v>129427254</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>92046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560066</v>
+        <v>560321</v>
       </c>
       <c r="R24" t="n">
-        <v>7064318</v>
+        <v>7064226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,19 +2997,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,44 +3014,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B25" t="n">
-        <v>92041</v>
+        <v>80186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R25" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B26" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,34 +3134,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,9 +3191,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
         <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>97015</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>97020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,57 +4043,61 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129427240</v>
+        <v>129424136</v>
       </c>
       <c r="B35" t="n">
-        <v>91552</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560201</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7064160</v>
+        <v>7064312</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,9 +4127,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,22 +4154,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129420535</v>
+        <v>129422985</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,21 +4177,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4187,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560216</v>
+        <v>560263</v>
       </c>
       <c r="R36" t="n">
-        <v>7064197</v>
+        <v>7064243</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4236,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4232,7 +4246,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4259,45 +4273,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129422985</v>
+        <v>129427246</v>
       </c>
       <c r="B37" t="n">
-        <v>91584</v>
+        <v>80215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560263</v>
+        <v>560192</v>
       </c>
       <c r="R37" t="n">
-        <v>7064243</v>
+        <v>7064186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,19 +4341,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,57 +4358,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427246</v>
+        <v>129423749</v>
       </c>
       <c r="B38" t="n">
-        <v>80210</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560192</v>
+        <v>560086</v>
       </c>
       <c r="R38" t="n">
-        <v>7064186</v>
+        <v>7064365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,9 +4438,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,22 +4465,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129423749</v>
+        <v>129420535</v>
       </c>
       <c r="B39" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,34 +4488,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560086</v>
+        <v>560216</v>
       </c>
       <c r="R39" t="n">
-        <v>7064365</v>
+        <v>7064197</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4547,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4543,7 +4557,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4570,49 +4584,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129424136</v>
+        <v>129427240</v>
       </c>
       <c r="B40" t="n">
-        <v>98769</v>
+        <v>91557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560048</v>
+        <v>560201</v>
       </c>
       <c r="R40" t="n">
-        <v>7064312</v>
+        <v>7064160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4642,19 +4652,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,12 +4669,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4684,7 +4684,7 @@
         <v>129427288</v>
       </c>
       <c r="B41" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4895,45 +4895,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427257</v>
+        <v>129427266</v>
       </c>
       <c r="B43" t="n">
-        <v>91886</v>
+        <v>57840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560200</v>
+        <v>560311</v>
       </c>
       <c r="R43" t="n">
-        <v>7064167</v>
+        <v>7064217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,45 +4996,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427265</v>
+        <v>129427273</v>
       </c>
       <c r="B44" t="n">
-        <v>80217</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560192</v>
+        <v>560001</v>
       </c>
       <c r="R44" t="n">
-        <v>7064186</v>
+        <v>7064286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5071,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5089,45 +5098,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427268</v>
+        <v>129423125</v>
       </c>
       <c r="B45" t="n">
-        <v>78833</v>
+        <v>98774</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559964</v>
+        <v>560204</v>
       </c>
       <c r="R45" t="n">
-        <v>7064339</v>
+        <v>7064212</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,9 +5170,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5174,22 +5197,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427273</v>
+        <v>129423615</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5216,19 +5239,19 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560001</v>
+        <v>560077</v>
       </c>
       <c r="R46" t="n">
-        <v>7064286</v>
+        <v>7064315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,79 +5281,84 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129423125</v>
+        <v>129427257</v>
       </c>
       <c r="B47" t="n">
-        <v>98769</v>
+        <v>91891</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560204</v>
+        <v>560200</v>
       </c>
       <c r="R47" t="n">
-        <v>7064212</v>
+        <v>7064167</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5360,19 +5388,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5387,61 +5405,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129423615</v>
+        <v>129427265</v>
       </c>
       <c r="B48" t="n">
-        <v>98769</v>
+        <v>80222</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560077</v>
+        <v>560192</v>
       </c>
       <c r="R48" t="n">
-        <v>7064315</v>
+        <v>7064186</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5471,19 +5485,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5498,61 +5502,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427266</v>
+        <v>129427268</v>
       </c>
       <c r="B49" t="n">
-        <v>57840</v>
+        <v>78838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560311</v>
+        <v>559964</v>
       </c>
       <c r="R49" t="n">
-        <v>7064217</v>
+        <v>7064339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,45 +5611,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129421945</v>
+        <v>129422827</v>
       </c>
       <c r="B50" t="n">
-        <v>92306</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560235</v>
+        <v>560315</v>
       </c>
       <c r="R50" t="n">
-        <v>7064180</v>
+        <v>7064259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,7 +5686,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5691,7 +5696,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5718,50 +5723,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422827</v>
+        <v>129423514</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560315</v>
+        <v>560095</v>
       </c>
       <c r="R51" t="n">
-        <v>7064259</v>
+        <v>7064302</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5793,7 +5797,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5803,7 +5807,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5830,30 +5834,34 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422999</v>
+        <v>129421945</v>
       </c>
       <c r="B52" t="n">
-        <v>91608</v>
+        <v>92311</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5861,10 +5869,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560298</v>
+        <v>560235</v>
       </c>
       <c r="R52" t="n">
-        <v>7064242</v>
+        <v>7064180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5904,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5914,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5933,49 +5941,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129423514</v>
+        <v>129422999</v>
       </c>
       <c r="B53" t="n">
-        <v>98769</v>
+        <v>91613</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560095</v>
+        <v>560298</v>
       </c>
       <c r="R53" t="n">
-        <v>7064302</v>
+        <v>7064242</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1292,50 +1292,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129422931</v>
+        <v>129427269</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560279</v>
+        <v>560091</v>
       </c>
       <c r="R8" t="n">
-        <v>7064267</v>
+        <v>7064300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,93 +1364,80 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129424015</v>
+        <v>129422931</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560049</v>
+        <v>560279</v>
       </c>
       <c r="R9" t="n">
-        <v>7064357</v>
+        <v>7064267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1493,7 +1479,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129427269</v>
+        <v>129424015</v>
       </c>
       <c r="B10" t="n">
         <v>98774</v>
@@ -1550,19 +1541,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560091</v>
+        <v>560049</v>
       </c>
       <c r="R10" t="n">
-        <v>7064300</v>
+        <v>7064357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,30 +1583,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427249</v>
+        <v>129424172</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,34 +1823,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560236</v>
+        <v>560042</v>
       </c>
       <c r="R13" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,14 +1880,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,12 +1907,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2011,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129424172</v>
+        <v>129427249</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,34 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560042</v>
+        <v>560236</v>
       </c>
       <c r="R15" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,19 +2084,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,22 +2106,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129422438</v>
+        <v>129427282</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560245</v>
+        <v>560033</v>
       </c>
       <c r="R16" t="n">
-        <v>7064205</v>
+        <v>7064272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,19 +2186,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427282</v>
+        <v>129427260</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R17" t="n">
-        <v>7064272</v>
+        <v>7064373</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427260</v>
+        <v>129427256</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559954</v>
+        <v>560241</v>
       </c>
       <c r="R18" t="n">
-        <v>7064373</v>
+        <v>7064201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,11 +2388,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B19" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,34 +2425,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R19" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,9 +2482,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,12 +2509,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2623,45 +2623,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427287</v>
+        <v>129427270</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560090</v>
+        <v>560092</v>
       </c>
       <c r="R21" t="n">
-        <v>7064325</v>
+        <v>7064308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2706,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129419985</v>
+        <v>129427287</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2751,17 +2756,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560212</v>
+        <v>560090</v>
       </c>
       <c r="R22" t="n">
-        <v>7064155</v>
+        <v>7064325</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,19 +2793,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,64 +2810,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R23" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2899,30 +2890,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B25" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,34 +3037,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R25" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,9 +3094,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3111,22 +3121,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129424097</v>
+        <v>129427263</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3134,34 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560066</v>
+        <v>560037</v>
       </c>
       <c r="R26" t="n">
-        <v>7064318</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,19 +3201,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>97020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>97020</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,61 +4043,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129424136</v>
+        <v>129422985</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>91589</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560263</v>
       </c>
       <c r="R35" t="n">
-        <v>7064312</v>
+        <v>7064243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,7 +4125,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4139,7 +4135,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4166,45 +4162,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129422985</v>
+        <v>129427240</v>
       </c>
       <c r="B36" t="n">
-        <v>91589</v>
+        <v>91557</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560263</v>
+        <v>560201</v>
       </c>
       <c r="R36" t="n">
-        <v>7064243</v>
+        <v>7064160</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4234,19 +4230,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4261,12 +4247,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4584,45 +4570,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129427240</v>
+        <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>91557</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560201</v>
+        <v>560048</v>
       </c>
       <c r="R40" t="n">
-        <v>7064160</v>
+        <v>7064312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,9 +4642,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,12 +4669,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4895,49 +4895,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427266</v>
+        <v>129427257</v>
       </c>
       <c r="B43" t="n">
-        <v>57840</v>
+        <v>91891</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560311</v>
+        <v>560200</v>
       </c>
       <c r="R43" t="n">
-        <v>7064217</v>
+        <v>7064167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,49 +4992,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427273</v>
+        <v>129427265</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>80222</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560001</v>
+        <v>560192</v>
       </c>
       <c r="R44" t="n">
-        <v>7064286</v>
+        <v>7064186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5071,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5098,49 +5089,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129423125</v>
+        <v>129427266</v>
       </c>
       <c r="B45" t="n">
-        <v>98774</v>
+        <v>57840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560204</v>
+        <v>560311</v>
       </c>
       <c r="R45" t="n">
-        <v>7064212</v>
+        <v>7064217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,19 +5161,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5197,19 +5178,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129423615</v>
+        <v>129423125</v>
       </c>
       <c r="B46" t="n">
         <v>98774</v>
@@ -5239,19 +5220,19 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560077</v>
+        <v>560204</v>
       </c>
       <c r="R46" t="n">
-        <v>7064315</v>
+        <v>7064212</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5283,7 +5264,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5293,7 +5274,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5320,45 +5301,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427257</v>
+        <v>129423615</v>
       </c>
       <c r="B47" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560200</v>
+        <v>560077</v>
       </c>
       <c r="R47" t="n">
-        <v>7064167</v>
+        <v>7064315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5388,9 +5373,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5405,57 +5400,61 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427265</v>
+        <v>129427273</v>
       </c>
       <c r="B48" t="n">
-        <v>80222</v>
+        <v>98774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560192</v>
+        <v>560001</v>
       </c>
       <c r="R48" t="n">
-        <v>7064186</v>
+        <v>7064286</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5496,6 +5495,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5611,50 +5611,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129422827</v>
+        <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>92311</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560315</v>
+        <v>560235</v>
       </c>
       <c r="R50" t="n">
-        <v>7064259</v>
+        <v>7064180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,7 +5681,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5696,7 +5691,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5723,49 +5718,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129423514</v>
+        <v>129422999</v>
       </c>
       <c r="B51" t="n">
-        <v>98774</v>
+        <v>91613</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560095</v>
+        <v>560298</v>
       </c>
       <c r="R51" t="n">
-        <v>7064302</v>
+        <v>7064242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5797,7 +5784,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5807,7 +5794,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5834,45 +5821,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129421945</v>
+        <v>129422827</v>
       </c>
       <c r="B52" t="n">
-        <v>92311</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560235</v>
+        <v>560315</v>
       </c>
       <c r="R52" t="n">
-        <v>7064180</v>
+        <v>7064259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5904,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5914,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5941,41 +5933,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>91613</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R53" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1292,49 +1292,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427269</v>
+        <v>129422931</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560091</v>
+        <v>560279</v>
       </c>
       <c r="R8" t="n">
-        <v>7064300</v>
+        <v>7064267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,80 +1365,93 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129422931</v>
+        <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560279</v>
+        <v>560049</v>
       </c>
       <c r="R9" t="n">
-        <v>7064267</v>
+        <v>7064357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1483,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,12 +1493,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129424015</v>
+        <v>129427269</v>
       </c>
       <c r="B10" t="n">
         <v>98774</v>
@@ -1541,19 +1550,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560049</v>
+        <v>560091</v>
       </c>
       <c r="R10" t="n">
-        <v>7064357</v>
+        <v>7064300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,39 +1592,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427267</v>
+        <v>129427249</v>
       </c>
       <c r="B12" t="n">
-        <v>92012</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,16 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560309</v>
+        <v>560236</v>
       </c>
       <c r="R12" t="n">
-        <v>7064195</v>
+        <v>7064186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,13 +1792,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1812,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129424172</v>
+        <v>129427264</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,34 +1832,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560042</v>
+        <v>560192</v>
       </c>
       <c r="R13" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,19 +1889,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,22 +1906,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129424172</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1929,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560042</v>
       </c>
       <c r="R14" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,9 +1986,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,22 +2013,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>92012</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,21 +2036,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R15" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,17 +2093,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427260</v>
+        <v>129427256</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559954</v>
+        <v>560241</v>
       </c>
       <c r="R17" t="n">
-        <v>7064373</v>
+        <v>7064201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427256</v>
+        <v>129422438</v>
       </c>
       <c r="B18" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,34 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560241</v>
+        <v>560245</v>
       </c>
       <c r="R18" t="n">
-        <v>7064201</v>
+        <v>7064205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,9 +2380,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,22 +2407,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129422438</v>
+        <v>129427260</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,34 +2430,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560245</v>
+        <v>559954</v>
       </c>
       <c r="R19" t="n">
-        <v>7064205</v>
+        <v>7064373</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,19 +2487,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,12 +2509,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2623,49 +2623,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129427270</v>
+        <v>129427287</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560092</v>
+        <v>560090</v>
       </c>
       <c r="R21" t="n">
-        <v>7064308</v>
+        <v>7064325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,7 +2702,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2725,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427287</v>
+        <v>129419985</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2756,17 +2751,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560090</v>
+        <v>560212</v>
       </c>
       <c r="R22" t="n">
-        <v>7064325</v>
+        <v>7064155</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2793,9 +2788,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,60 +2815,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R23" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2890,39 +2899,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129424097</v>
+        <v>129427263</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,34 +3037,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560066</v>
+        <v>560037</v>
       </c>
       <c r="R25" t="n">
-        <v>7064318</v>
+        <v>7064364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,19 +3094,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,22 +3111,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B26" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,34 +3134,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,9 +3191,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R31" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3749,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,21 +3765,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R32" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3820,11 +3825,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>97020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,57 +4043,61 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129422985</v>
+        <v>129424136</v>
       </c>
       <c r="B35" t="n">
-        <v>91589</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560263</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7064243</v>
+        <v>7064312</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,7 +4129,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4135,7 +4139,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4259,45 +4263,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427246</v>
+        <v>129422985</v>
       </c>
       <c r="B37" t="n">
-        <v>80215</v>
+        <v>91589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560192</v>
+        <v>560263</v>
       </c>
       <c r="R37" t="n">
-        <v>7064186</v>
+        <v>7064243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,9 +4331,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4344,57 +4358,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B38" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R38" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,19 +4438,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,22 +4455,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,34 +4478,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R39" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4537,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4543,7 +4547,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4570,49 +4574,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129424136</v>
+        <v>129420535</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560048</v>
+        <v>560216</v>
       </c>
       <c r="R40" t="n">
-        <v>7064312</v>
+        <v>7064197</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5089,49 +5089,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427266</v>
+        <v>129427268</v>
       </c>
       <c r="B45" t="n">
-        <v>57840</v>
+        <v>78838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560311</v>
+        <v>559964</v>
       </c>
       <c r="R45" t="n">
-        <v>7064217</v>
+        <v>7064339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5190,49 +5186,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129423125</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>57840</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560204</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064212</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5262,19 +5258,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5289,19 +5275,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129423615</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
         <v>98774</v>
@@ -5331,19 +5317,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560077</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064315</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5373,46 +5359,37 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129427273</v>
+        <v>129423125</v>
       </c>
       <c r="B48" t="n">
         <v>98774</v>
@@ -5442,19 +5419,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560001</v>
+        <v>560204</v>
       </c>
       <c r="R48" t="n">
-        <v>7064286</v>
+        <v>7064212</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,75 +5461,88 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129427268</v>
+        <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>559964</v>
+        <v>560077</v>
       </c>
       <c r="R49" t="n">
-        <v>7064339</v>
+        <v>7064315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5582,9 +5572,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,12 +5599,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,45 +1098,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129427243</v>
+        <v>129424015</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560198</v>
+        <v>560049</v>
       </c>
       <c r="R6" t="n">
-        <v>7064162</v>
+        <v>7064357</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1170,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,57 +1197,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427283</v>
+        <v>129427269</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559968</v>
+        <v>560091</v>
       </c>
       <c r="R7" t="n">
-        <v>7064298</v>
+        <v>7064300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,6 +1292,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1292,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129422931</v>
+        <v>129427243</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,39 +1322,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560279</v>
+        <v>560198</v>
       </c>
       <c r="R8" t="n">
-        <v>7064267</v>
+        <v>7064162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,24 +1379,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,61 +1396,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129424015</v>
+        <v>129427283</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560049</v>
+        <v>559968</v>
       </c>
       <c r="R9" t="n">
-        <v>7064357</v>
+        <v>7064298</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,19 +1476,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,61 +1493,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129427269</v>
+        <v>129422931</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560091</v>
+        <v>560279</v>
       </c>
       <c r="R10" t="n">
-        <v>7064300</v>
+        <v>7064267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,30 +1578,44 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427249</v>
+        <v>129424172</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560236</v>
+        <v>560042</v>
       </c>
       <c r="R12" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,14 +1787,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,22 +1814,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R13" t="n">
         <v>7064186</v>
@@ -1892,6 +1897,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129424172</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,34 +1939,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560042</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,19 +1996,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,12 +2013,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427282</v>
+        <v>129422438</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560033</v>
+        <v>560245</v>
       </c>
       <c r="R16" t="n">
-        <v>7064272</v>
+        <v>7064205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,9 +2186,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2203,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427256</v>
+        <v>129427282</v>
       </c>
       <c r="B17" t="n">
-        <v>91891</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560241</v>
+        <v>560033</v>
       </c>
       <c r="R17" t="n">
-        <v>7064201</v>
+        <v>7064272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129422438</v>
+        <v>129427260</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560245</v>
+        <v>559954</v>
       </c>
       <c r="R18" t="n">
-        <v>7064205</v>
+        <v>7064373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,19 +2390,14 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:52</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,57 +2412,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R19" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,17 +2501,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,49 +2526,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427271</v>
+        <v>129427256</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560086</v>
+        <v>560241</v>
       </c>
       <c r="R20" t="n">
-        <v>7064325</v>
+        <v>7064201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,7 +2605,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B25" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,34 +3037,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R25" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,9 +3094,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3111,22 +3121,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129424097</v>
+        <v>129427263</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3134,34 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560066</v>
+        <v>560037</v>
       </c>
       <c r="R26" t="n">
-        <v>7064318</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,19 +3201,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,12 +3218,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R31" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3723,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,10 +3749,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R32" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,6 +3820,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>97020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R33" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,19 +3919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,22 +3936,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B34" t="n">
-        <v>97020</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,34 +3959,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R34" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,9 +4016,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,61 +4043,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129424136</v>
+        <v>129420535</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560216</v>
       </c>
       <c r="R35" t="n">
-        <v>7064312</v>
+        <v>7064197</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,7 +4125,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4139,7 +4135,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4166,45 +4162,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427240</v>
+        <v>129422985</v>
       </c>
       <c r="B36" t="n">
-        <v>91557</v>
+        <v>91589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560201</v>
+        <v>560263</v>
       </c>
       <c r="R36" t="n">
-        <v>7064160</v>
+        <v>7064243</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4234,9 +4230,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,57 +4257,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129422985</v>
+        <v>129427240</v>
       </c>
       <c r="B37" t="n">
-        <v>91589</v>
+        <v>91557</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560263</v>
+        <v>560201</v>
       </c>
       <c r="R37" t="n">
-        <v>7064243</v>
+        <v>7064160</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,19 +4337,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4358,12 +4354,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4574,45 +4570,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129420535</v>
+        <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560216</v>
+        <v>560048</v>
       </c>
       <c r="R40" t="n">
-        <v>7064197</v>
+        <v>7064312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4992,32 +4992,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129427265</v>
+        <v>129427268</v>
       </c>
       <c r="B44" t="n">
-        <v>80222</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560192</v>
+        <v>559964</v>
       </c>
       <c r="R44" t="n">
-        <v>7064186</v>
+        <v>7064339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,32 +5089,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427268</v>
+        <v>129427265</v>
       </c>
       <c r="B45" t="n">
-        <v>78838</v>
+        <v>80222</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>559964</v>
+        <v>560192</v>
       </c>
       <c r="R45" t="n">
-        <v>7064339</v>
+        <v>7064186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,49 +1098,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129424015</v>
+        <v>129422931</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560049</v>
+        <v>560279</v>
       </c>
       <c r="R6" t="n">
-        <v>7064357</v>
+        <v>7064267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,49 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427269</v>
+        <v>129427243</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560091</v>
+        <v>560198</v>
       </c>
       <c r="R7" t="n">
-        <v>7064300</v>
+        <v>7064162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R8" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,45 +1409,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129427283</v>
+        <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559968</v>
+        <v>560049</v>
       </c>
       <c r="R9" t="n">
-        <v>7064298</v>
+        <v>7064357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,9 +1481,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,62 +1508,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129422931</v>
+        <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560279</v>
+        <v>560091</v>
       </c>
       <c r="R10" t="n">
-        <v>7064267</v>
+        <v>7064300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,44 +1592,30 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129424172</v>
+        <v>129427267</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>92016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560042</v>
+        <v>560309</v>
       </c>
       <c r="R12" t="n">
-        <v>7064308</v>
+        <v>7064195</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,49 +1782,40 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427249</v>
+        <v>129427264</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,7 +1847,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560236</v>
+        <v>560192</v>
       </c>
       <c r="R13" t="n">
         <v>7064186</v>
@@ -1897,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129424172</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,34 +1920,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560042</v>
       </c>
       <c r="R14" t="n">
-        <v>7064186</v>
+        <v>7064308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,9 +1977,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427267</v>
+        <v>129427249</v>
       </c>
       <c r="B15" t="n">
-        <v>92012</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,16 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560309</v>
+        <v>560236</v>
       </c>
       <c r="R15" t="n">
-        <v>7064195</v>
+        <v>7064186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,13 +2089,17 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129422438</v>
+        <v>129427256</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>91895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560245</v>
+        <v>560241</v>
       </c>
       <c r="R16" t="n">
-        <v>7064205</v>
+        <v>7064201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,19 +2186,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129427282</v>
+        <v>129422438</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,34 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560033</v>
+        <v>560245</v>
       </c>
       <c r="R17" t="n">
-        <v>7064272</v>
+        <v>7064205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,9 +2283,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,22 +2310,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427260</v>
+        <v>129427282</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R18" t="n">
-        <v>7064373</v>
+        <v>7064272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,7 +2422,7 @@
         <v>129427271</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427256</v>
+        <v>129427260</v>
       </c>
       <c r="B20" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560241</v>
+        <v>559954</v>
       </c>
       <c r="R20" t="n">
-        <v>7064201</v>
+        <v>7064373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,6 +2592,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,48 +2720,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R22" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,91 +2792,78 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R23" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2899,62 +2890,71 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427254</v>
+        <v>129427263</v>
       </c>
       <c r="B24" t="n">
-        <v>92046</v>
+        <v>80186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560321</v>
+        <v>560037</v>
       </c>
       <c r="R24" t="n">
-        <v>7064226</v>
+        <v>7064364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129427263</v>
+        <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>80186</v>
+        <v>92050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560037</v>
+        <v>560321</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,45 +3230,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129427235</v>
+        <v>129424195</v>
       </c>
       <c r="B27" t="n">
-        <v>97020</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560199</v>
+        <v>560020</v>
       </c>
       <c r="R27" t="n">
-        <v>7064182</v>
+        <v>7064291</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,9 +3302,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3315,61 +3329,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129424195</v>
+        <v>129427235</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>97024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560020</v>
+        <v>560199</v>
       </c>
       <c r="R28" t="n">
-        <v>7064291</v>
+        <v>7064182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,19 +3409,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
         <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R31" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3749,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,21 +3765,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R32" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3820,11 +3825,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3854,7 +3854,7 @@
         <v>129427234</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129420535</v>
+        <v>129422985</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560216</v>
+        <v>560263</v>
       </c>
       <c r="R35" t="n">
-        <v>7064197</v>
+        <v>7064243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4162,45 +4162,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129422985</v>
+        <v>129427240</v>
       </c>
       <c r="B36" t="n">
-        <v>91589</v>
+        <v>91561</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560263</v>
+        <v>560201</v>
       </c>
       <c r="R36" t="n">
-        <v>7064243</v>
+        <v>7064160</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,19 +4230,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4257,22 +4247,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427240</v>
+        <v>129427246</v>
       </c>
       <c r="B37" t="n">
-        <v>91557</v>
+        <v>80215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4280,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4304,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560201</v>
+        <v>560192</v>
       </c>
       <c r="R37" t="n">
-        <v>7064160</v>
+        <v>7064186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4366,45 +4356,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427246</v>
+        <v>129423749</v>
       </c>
       <c r="B38" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560192</v>
+        <v>560086</v>
       </c>
       <c r="R38" t="n">
-        <v>7064186</v>
+        <v>7064365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,9 +4424,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,22 +4451,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129423749</v>
+        <v>129420535</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,34 +4474,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560086</v>
+        <v>560216</v>
       </c>
       <c r="R39" t="n">
-        <v>7064365</v>
+        <v>7064197</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4573,7 +4573,7 @@
         <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,32 +4895,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129427257</v>
+        <v>129427265</v>
       </c>
       <c r="B43" t="n">
-        <v>91891</v>
+        <v>80222</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560200</v>
+        <v>560192</v>
       </c>
       <c r="R43" t="n">
-        <v>7064167</v>
+        <v>7064186</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,45 +5089,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427265</v>
+        <v>129427273</v>
       </c>
       <c r="B45" t="n">
-        <v>80222</v>
+        <v>98778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560192</v>
+        <v>560001</v>
       </c>
       <c r="R45" t="n">
-        <v>7064186</v>
+        <v>7064286</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5168,6 +5172,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5186,49 +5191,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427266</v>
+        <v>129427257</v>
       </c>
       <c r="B46" t="n">
-        <v>57840</v>
+        <v>91895</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560311</v>
+        <v>560200</v>
       </c>
       <c r="R46" t="n">
-        <v>7064217</v>
+        <v>7064167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,37 +5288,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427273</v>
+        <v>129427266</v>
       </c>
       <c r="B47" t="n">
-        <v>98774</v>
+        <v>57840</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5326,10 +5327,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560001</v>
+        <v>560311</v>
       </c>
       <c r="R47" t="n">
-        <v>7064286</v>
+        <v>7064217</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5370,7 +5371,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5718,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129422999</v>
+        <v>129422827</v>
       </c>
       <c r="B51" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5729,30 +5729,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560298</v>
+        <v>560315</v>
       </c>
       <c r="R51" t="n">
-        <v>7064242</v>
+        <v>7064259</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,7 +5793,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5794,7 +5803,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5821,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422827</v>
+        <v>129422999</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>91617</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,39 +5841,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560315</v>
+        <v>560298</v>
       </c>
       <c r="R52" t="n">
-        <v>7064259</v>
+        <v>7064242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5936,7 +5936,7 @@
         <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129422931</v>
+        <v>129427243</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560279</v>
+        <v>560198</v>
       </c>
       <c r="R6" t="n">
-        <v>7064267</v>
+        <v>7064162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,24 +1166,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129427243</v>
+        <v>129427283</v>
       </c>
       <c r="B7" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560198</v>
+        <v>559968</v>
       </c>
       <c r="R7" t="n">
-        <v>7064162</v>
+        <v>7064298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129427283</v>
+        <v>129422931</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1303,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559968</v>
+        <v>560279</v>
       </c>
       <c r="R8" t="n">
-        <v>7064298</v>
+        <v>7064267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,9 +1365,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>129424015</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129427269</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129427267</v>
+        <v>129424172</v>
       </c>
       <c r="B12" t="n">
-        <v>92016</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,29 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560309</v>
+        <v>560042</v>
       </c>
       <c r="R12" t="n">
-        <v>7064195</v>
+        <v>7064308</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,40 +1787,49 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,7 +1861,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R13" t="n">
         <v>7064186</v>
@@ -1883,6 +1897,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129424172</v>
+        <v>129427264</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,34 +1939,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560042</v>
+        <v>560192</v>
       </c>
       <c r="R14" t="n">
-        <v>7064308</v>
+        <v>7064186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,19 +1996,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,22 +2013,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>92018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,21 +2036,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R15" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,17 +2093,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427256</v>
+        <v>129427260</v>
       </c>
       <c r="B16" t="n">
-        <v>91895</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560241</v>
+        <v>559954</v>
       </c>
       <c r="R16" t="n">
-        <v>7064201</v>
+        <v>7064373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,7 +2223,7 @@
         <v>129422438</v>
       </c>
       <c r="B17" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427282</v>
+        <v>129427256</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>91897</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560033</v>
+        <v>560241</v>
       </c>
       <c r="R18" t="n">
-        <v>7064272</v>
+        <v>7064201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,49 +2424,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427271</v>
+        <v>129427282</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560086</v>
+        <v>560033</v>
       </c>
       <c r="R19" t="n">
-        <v>7064325</v>
+        <v>7064272</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,7 +2503,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,45 +2521,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427260</v>
+        <v>129427271</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559954</v>
+        <v>560086</v>
       </c>
       <c r="R20" t="n">
-        <v>7064373</v>
+        <v>7064325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,17 +2598,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2720,52 +2720,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R22" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2792,78 +2788,91 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R23" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2890,49 +2899,40 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427263</v>
+        <v>129424097</v>
       </c>
       <c r="B24" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560037</v>
+        <v>560066</v>
       </c>
       <c r="R24" t="n">
-        <v>7064364</v>
+        <v>7064318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2997,9 +2997,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3014,22 +3024,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129424097</v>
+        <v>129427263</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,34 +3047,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560066</v>
+        <v>560037</v>
       </c>
       <c r="R25" t="n">
-        <v>7064318</v>
+        <v>7064364</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,19 +3104,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,12 +3121,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
         <v>129427254</v>
       </c>
       <c r="B26" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,49 +3230,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129424195</v>
+        <v>129427235</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>97026</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560020</v>
+        <v>560199</v>
       </c>
       <c r="R27" t="n">
-        <v>7064291</v>
+        <v>7064182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3302,19 +3298,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3329,57 +3315,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129427235</v>
+        <v>129424195</v>
       </c>
       <c r="B28" t="n">
-        <v>97024</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560199</v>
+        <v>560020</v>
       </c>
       <c r="R28" t="n">
-        <v>7064182</v>
+        <v>7064291</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3409,9 +3399,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
         <v>129427242</v>
       </c>
       <c r="B29" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129427250</v>
+        <v>129427284</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560233</v>
+        <v>559972</v>
       </c>
       <c r="R31" t="n">
-        <v>7064178</v>
+        <v>7064368</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3723,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,10 +3749,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129427284</v>
+        <v>129427250</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559972</v>
+        <v>560233</v>
       </c>
       <c r="R32" t="n">
-        <v>7064368</v>
+        <v>7064178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,6 +3820,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129427234</v>
+        <v>129423735</v>
       </c>
       <c r="B33" t="n">
-        <v>97024</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,34 +3862,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560205</v>
+        <v>560080</v>
       </c>
       <c r="R33" t="n">
-        <v>7064195</v>
+        <v>7064344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,9 +3919,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129423735</v>
+        <v>129427234</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>97026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,34 +3969,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560080</v>
+        <v>560205</v>
       </c>
       <c r="R34" t="n">
-        <v>7064344</v>
+        <v>7064195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,19 +4026,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,57 +4043,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129422985</v>
+        <v>129427240</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>91563</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560263</v>
+        <v>560201</v>
       </c>
       <c r="R35" t="n">
-        <v>7064243</v>
+        <v>7064160</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,19 +4123,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4150,57 +4140,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427240</v>
+        <v>129422985</v>
       </c>
       <c r="B36" t="n">
-        <v>91561</v>
+        <v>91595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560201</v>
+        <v>560263</v>
       </c>
       <c r="R36" t="n">
-        <v>7064160</v>
+        <v>7064243</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,9 +4220,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,57 +4247,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427246</v>
+        <v>129420535</v>
       </c>
       <c r="B37" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560192</v>
+        <v>560216</v>
       </c>
       <c r="R37" t="n">
-        <v>7064186</v>
+        <v>7064197</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,9 +4327,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4344,57 +4354,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129423749</v>
+        <v>129427246</v>
       </c>
       <c r="B38" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560086</v>
+        <v>560192</v>
       </c>
       <c r="R38" t="n">
-        <v>7064365</v>
+        <v>7064186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,19 +4434,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,22 +4451,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129420535</v>
+        <v>129423749</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,34 +4474,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560216</v>
+        <v>560086</v>
       </c>
       <c r="R39" t="n">
-        <v>7064197</v>
+        <v>7064365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4573,7 +4573,7 @@
         <v>129424136</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5089,49 +5089,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129427273</v>
+        <v>129427257</v>
       </c>
       <c r="B45" t="n">
-        <v>98778</v>
+        <v>91897</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560001</v>
+        <v>560200</v>
       </c>
       <c r="R45" t="n">
-        <v>7064286</v>
+        <v>7064167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,7 +5168,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5191,45 +5186,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129427257</v>
+        <v>129427266</v>
       </c>
       <c r="B46" t="n">
-        <v>91895</v>
+        <v>57840</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560200</v>
+        <v>560311</v>
       </c>
       <c r="R46" t="n">
-        <v>7064167</v>
+        <v>7064217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5288,37 +5287,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129427266</v>
+        <v>129427273</v>
       </c>
       <c r="B47" t="n">
-        <v>57840</v>
+        <v>98780</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5327,10 +5326,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560311</v>
+        <v>560001</v>
       </c>
       <c r="R47" t="n">
-        <v>7064217</v>
+        <v>7064286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,6 +5370,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>129423125</v>
       </c>
       <c r="B48" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>129423615</v>
       </c>
       <c r="B49" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>129421945</v>
       </c>
       <c r="B50" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>129422999</v>
       </c>
       <c r="B52" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>129423514</v>
       </c>
       <c r="B53" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 34297-2025 artfynd.xlsx
+++ b/artfynd/A 34297-2025 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129427249</v>
+        <v>129427267</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>92018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,21 +1837,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560236</v>
+        <v>560309</v>
       </c>
       <c r="R13" t="n">
-        <v>7064186</v>
+        <v>7064195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,17 +1894,13 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1928,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427264</v>
+        <v>129427249</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,7 +1954,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560192</v>
+        <v>560236</v>
       </c>
       <c r="R14" t="n">
         <v>7064186</v>
@@ -1999,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427267</v>
+        <v>129427264</v>
       </c>
       <c r="B15" t="n">
-        <v>92018</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,16 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560309</v>
+        <v>560192</v>
       </c>
       <c r="R15" t="n">
-        <v>7064195</v>
+        <v>7064186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,7 +2100,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2720,48 +2720,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129419985</v>
+        <v>129427270</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560212</v>
+        <v>560092</v>
       </c>
       <c r="R22" t="n">
-        <v>7064155</v>
+        <v>7064308</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,91 +2792,78 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427270</v>
+        <v>129419985</v>
       </c>
       <c r="B23" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560092</v>
+        <v>560212</v>
       </c>
       <c r="R23" t="n">
-        <v>7064308</v>
+        <v>7064155</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2899,30 +2890,39 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4055,45 +4055,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129427240</v>
+        <v>129424136</v>
       </c>
       <c r="B35" t="n">
-        <v>91563</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560201</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7064160</v>
+        <v>7064312</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,9 +4127,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,12 +4154,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4259,45 +4273,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129420535</v>
+        <v>129427246</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560216</v>
+        <v>560192</v>
       </c>
       <c r="R37" t="n">
-        <v>7064197</v>
+        <v>7064186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,19 +4341,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,57 +4358,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427246</v>
+        <v>129423749</v>
       </c>
       <c r="B38" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560192</v>
+        <v>560086</v>
       </c>
       <c r="R38" t="n">
-        <v>7064186</v>
+        <v>7064365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,9 +4438,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,57 +4465,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129423749</v>
+        <v>129427240</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560086</v>
+        <v>560201</v>
       </c>
       <c r="R39" t="n">
-        <v>7064365</v>
+        <v>7064160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4531,19 +4545,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,61 +4562,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129424136</v>
+        <v>129420535</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560048</v>
+        <v>560216</v>
       </c>
       <c r="R40" t="n">
-        <v>7064312</v>
+        <v>7064197</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5611,34 +5611,30 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129421945</v>
+        <v>129422999</v>
       </c>
       <c r="B50" t="n">
-        <v>92317</v>
+        <v>91619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5646,10 +5642,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560235</v>
+        <v>560298</v>
       </c>
       <c r="R50" t="n">
-        <v>7064180</v>
+        <v>7064242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,7 +5677,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5691,7 +5687,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,41 +5826,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129422999</v>
+        <v>129423514</v>
       </c>
       <c r="B52" t="n">
-        <v>91619</v>
+        <v>98780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hällrået, Hällrået, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560298</v>
+        <v>560095</v>
       </c>
       <c r="R52" t="n">
-        <v>7064242</v>
+        <v>7064302</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,7 +5900,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5906,7 +5910,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5933,49 +5937,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129423514</v>
+        <v>129421945</v>
       </c>
       <c r="B53" t="n">
-        <v>98780</v>
+        <v>92317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Hällrået, Hällrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560095</v>
+        <v>560235</v>
       </c>
       <c r="R53" t="n">
-        <v>7064302</v>
+        <v>7064180</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
